--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,38 +6510,38 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R31" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S31" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T31" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U31" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W31" t="n">
         <v>2.2</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X31" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z31" t="n">
         <v>8.9</v>
@@ -6550,103 +6550,103 @@
         <v>1.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG31" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH31" t="n">
         <v>1.09</v>
       </c>
       <c r="AI31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN31" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN31" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO31" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ31" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB31" t="n">
         <v>1.4</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD31" t="n">
         <v>2.62</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF31" t="n">
         <v>1.08</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46141.60416666666</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,38 +6707,38 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S32" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U32" t="n">
         <v>2.2</v>
       </c>
-      <c r="S32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V32" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W32" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X32" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z32" t="n">
         <v>8.9</v>
@@ -6747,103 +6747,103 @@
         <v>1.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG32" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH32" t="n">
         <v>1.09</v>
       </c>
       <c r="AI32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT32" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB32" t="n">
         <v>1.4</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD32" t="n">
         <v>2.62</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF32" t="n">
         <v>1.08</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46141.60416666666</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,38 +6510,38 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S31" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U31" t="n">
         <v>2.2</v>
       </c>
-      <c r="S31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U31" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V31" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W31" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X31" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z31" t="n">
         <v>8.9</v>
@@ -6550,103 +6550,103 @@
         <v>1.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG31" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH31" t="n">
         <v>1.09</v>
       </c>
       <c r="AI31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT31" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB31" t="n">
         <v>1.4</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD31" t="n">
         <v>2.62</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF31" t="n">
         <v>1.08</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46141.60416666666</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,38 +6707,38 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R32" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S32" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T32" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U32" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W32" t="n">
         <v>2.2</v>
       </c>
-      <c r="V32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X32" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z32" t="n">
         <v>8.9</v>
@@ -6747,103 +6747,103 @@
         <v>1.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG32" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH32" t="n">
         <v>1.09</v>
       </c>
       <c r="AI32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN32" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN32" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ32" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB32" t="n">
         <v>1.4</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD32" t="n">
         <v>2.62</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF32" t="n">
         <v>1.08</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,38 +6510,38 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R31" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S31" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T31" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U31" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W31" t="n">
         <v>2.2</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X31" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z31" t="n">
         <v>8.9</v>
@@ -6550,103 +6550,103 @@
         <v>1.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG31" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH31" t="n">
         <v>1.09</v>
       </c>
       <c r="AI31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN31" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN31" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO31" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ31" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB31" t="n">
         <v>1.4</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD31" t="n">
         <v>2.62</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF31" t="n">
         <v>1.08</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46141.60416666666</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,38 +6707,38 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S32" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U32" t="n">
         <v>2.2</v>
       </c>
-      <c r="S32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V32" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W32" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X32" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z32" t="n">
         <v>8.9</v>
@@ -6747,103 +6747,103 @@
         <v>1.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG32" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH32" t="n">
         <v>1.09</v>
       </c>
       <c r="AI32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT32" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB32" t="n">
         <v>1.4</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD32" t="n">
         <v>2.62</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF32" t="n">
         <v>1.08</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G39" t="n">

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7692,7 +7692,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,38 +6510,38 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S31" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U31" t="n">
         <v>2.2</v>
       </c>
-      <c r="S31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U31" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V31" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W31" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X31" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z31" t="n">
         <v>8.9</v>
@@ -6550,103 +6550,103 @@
         <v>1.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG31" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH31" t="n">
         <v>1.09</v>
       </c>
       <c r="AI31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT31" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB31" t="n">
         <v>1.4</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD31" t="n">
         <v>2.62</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF31" t="n">
         <v>1.08</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46141.60416666666</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,38 +6707,38 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R32" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S32" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T32" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U32" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W32" t="n">
         <v>2.2</v>
       </c>
-      <c r="V32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X32" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z32" t="n">
         <v>8.9</v>
@@ -6747,103 +6747,103 @@
         <v>1.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG32" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH32" t="n">
         <v>1.09</v>
       </c>
       <c r="AI32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN32" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN32" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ32" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB32" t="n">
         <v>1.4</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD32" t="n">
         <v>2.62</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF32" t="n">
         <v>1.08</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46141.60416666666</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G39" t="n">

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,38 +6510,38 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R31" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S31" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T31" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U31" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W31" t="n">
         <v>2.2</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X31" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z31" t="n">
         <v>8.9</v>
@@ -6550,103 +6550,103 @@
         <v>1.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG31" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH31" t="n">
         <v>1.09</v>
       </c>
       <c r="AI31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN31" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN31" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO31" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ31" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB31" t="n">
         <v>1.4</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD31" t="n">
         <v>2.62</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF31" t="n">
         <v>1.08</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46141.60416666666</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,38 +6707,38 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S32" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U32" t="n">
         <v>2.2</v>
       </c>
-      <c r="S32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V32" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W32" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X32" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z32" t="n">
         <v>8.9</v>
@@ -6747,103 +6747,103 @@
         <v>1.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG32" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH32" t="n">
         <v>1.09</v>
       </c>
       <c r="AI32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT32" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB32" t="n">
         <v>1.4</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD32" t="n">
         <v>2.62</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF32" t="n">
         <v>1.08</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46141.60416666666</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G39" t="n">

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,38 +6510,38 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S31" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U31" t="n">
         <v>2.2</v>
       </c>
-      <c r="S31" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U31" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V31" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W31" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X31" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z31" t="n">
         <v>8.9</v>
@@ -6550,103 +6550,103 @@
         <v>1.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG31" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH31" t="n">
         <v>1.09</v>
       </c>
       <c r="AI31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT31" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB31" t="n">
         <v>1.4</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD31" t="n">
         <v>2.62</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF31" t="n">
         <v>1.08</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46141.60416666666</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,38 +6707,38 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R32" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S32" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T32" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U32" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W32" t="n">
         <v>2.2</v>
       </c>
-      <c r="V32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X32" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z32" t="n">
         <v>8.9</v>
@@ -6747,103 +6747,103 @@
         <v>1.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG32" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH32" t="n">
         <v>1.09</v>
       </c>
       <c r="AI32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN32" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN32" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ32" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB32" t="n">
         <v>1.4</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD32" t="n">
         <v>2.62</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF32" t="n">
         <v>1.08</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G39" t="n">

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,38 +6510,38 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R31" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S31" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T31" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U31" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W31" t="n">
         <v>2.2</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X31" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z31" t="n">
         <v>8.9</v>
@@ -6550,103 +6550,103 @@
         <v>1.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG31" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH31" t="n">
         <v>1.09</v>
       </c>
       <c r="AI31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN31" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN31" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO31" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS31" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ31" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB31" t="n">
         <v>1.4</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD31" t="n">
         <v>2.62</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF31" t="n">
         <v>1.08</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
         <v>46141.60416666666</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,38 +6707,38 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S32" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U32" t="n">
         <v>2.2</v>
       </c>
-      <c r="S32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V32" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W32" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X32" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z32" t="n">
         <v>8.9</v>
@@ -6747,103 +6747,103 @@
         <v>1.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG32" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH32" t="n">
         <v>1.09</v>
       </c>
       <c r="AI32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT32" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB32" t="n">
         <v>1.4</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD32" t="n">
         <v>2.62</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF32" t="n">
         <v>1.08</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI42"/>
+  <dimension ref="A1:BI44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46141.58333333334</v>
+        <v>46141.57291666666</v>
       </c>
     </row>
     <row r="27">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6510,137 +6510,137 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46141.60416666666</v>
+        <v>46141.58333333334</v>
       </c>
     </row>
     <row r="32">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,138 +6904,138 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.02</v>
+        <v>3.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>10.2</v>
+        <v>2.9</v>
       </c>
       <c r="R33" t="n">
-        <v>28</v>
+        <v>2.2</v>
       </c>
       <c r="S33" t="n">
-        <v>1.32</v>
+        <v>4.3</v>
       </c>
       <c r="T33" t="n">
-        <v>3.65</v>
+        <v>1.77</v>
       </c>
       <c r="U33" t="n">
-        <v>18.5</v>
+        <v>3.11</v>
       </c>
       <c r="V33" t="n">
-        <v>1.15</v>
+        <v>1.59</v>
       </c>
       <c r="W33" t="n">
-        <v>4.75</v>
+        <v>2.2</v>
       </c>
       <c r="X33" t="n">
-        <v>1.77</v>
+        <v>3.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.1</v>
+        <v>8.9</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.07</v>
+        <v>1.62</v>
       </c>
       <c r="AD33" t="n">
-        <v>9.5</v>
+        <v>2.19</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.3</v>
+        <v>2.75</v>
       </c>
       <c r="AF33" t="n">
-        <v>3.4</v>
+        <v>1.4</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.54</v>
+        <v>5.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.19</v>
+        <v>1.09</v>
       </c>
       <c r="AI33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BD33" t="n">
         <v>2.62</v>
       </c>
-      <c r="AJ33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
+      <c r="BE33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BF33" t="n">
         <v>1.08</v>
       </c>
-      <c r="BC33" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BG33" t="n">
         <v>0</v>
       </c>
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46141.625</v>
+        <v>46141.60416666666</v>
       </c>
     </row>
     <row r="34">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46141.66666666666</v>
+        <v>46141.625</v>
       </c>
     </row>
     <row r="36">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7643,12 +7643,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,112 +7696,112 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.12</v>
+        <v>3.11</v>
       </c>
       <c r="Q37" t="n">
-        <v>8.5</v>
+        <v>3.39</v>
       </c>
       <c r="R37" t="n">
-        <v>21</v>
+        <v>2.51</v>
       </c>
       <c r="S37" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.41</v>
+        <v>1.96</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.54</v>
+        <v>1.75</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
         <v>0</v>
@@ -7810,19 +7810,19 @@
         <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46141.67708333334</v>
+        <v>46141.66666666666</v>
       </c>
     </row>
     <row r="38">
@@ -7840,27 +7840,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46141.83333333334</v>
+        <v>46141.66666666666</v>
       </c>
     </row>
     <row r="39">
@@ -8037,27 +8037,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,112 +8090,112 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ39" t="n">
         <v>0</v>
@@ -8204,19 +8204,19 @@
         <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46141.83333333334</v>
+        <v>46141.67708333334</v>
       </c>
     </row>
     <row r="40">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46141.875</v>
+        <v>46141.83333333334</v>
       </c>
     </row>
     <row r="41">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
-        <v>46141.91666666666</v>
+        <v>46141.83333333334</v>
       </c>
     </row>
     <row r="42">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8816,6 +8816,400 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
+        <v>46141.875</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tulsa Roughnecks</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI43" s="3" t="n">
+        <v>46141.91666666666</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Portland Thorns</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>San Diego Wave</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI44" s="3" t="n">
         <v>46141.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,38 +6707,38 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R32" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S32" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T32" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U32" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W32" t="n">
         <v>2.2</v>
       </c>
-      <c r="V32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X32" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z32" t="n">
         <v>8.9</v>
@@ -6747,103 +6747,103 @@
         <v>1.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG32" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH32" t="n">
         <v>1.09</v>
       </c>
       <c r="AI32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN32" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN32" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ32" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB32" t="n">
         <v>1.4</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD32" t="n">
         <v>2.62</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF32" t="n">
         <v>1.08</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46141.60416666666</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,38 +6904,38 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S33" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U33" t="n">
         <v>2.2</v>
       </c>
-      <c r="S33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U33" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V33" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W33" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X33" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z33" t="n">
         <v>8.9</v>
@@ -6944,103 +6944,103 @@
         <v>1.03</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG33" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH33" t="n">
         <v>1.09</v>
       </c>
       <c r="AI33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT33" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB33" t="n">
         <v>1.4</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD33" t="n">
         <v>2.62</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF33" t="n">
         <v>1.08</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI33" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G41" t="n">

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,38 +6707,38 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S32" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U32" t="n">
         <v>2.2</v>
       </c>
-      <c r="S32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V32" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W32" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X32" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z32" t="n">
         <v>8.9</v>
@@ -6747,103 +6747,103 @@
         <v>1.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG32" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH32" t="n">
         <v>1.09</v>
       </c>
       <c r="AI32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT32" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB32" t="n">
         <v>1.4</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD32" t="n">
         <v>2.62</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF32" t="n">
         <v>1.08</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46141.60416666666</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,38 +6904,38 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R33" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S33" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T33" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U33" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W33" t="n">
         <v>2.2</v>
       </c>
-      <c r="V33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X33" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z33" t="n">
         <v>8.9</v>
@@ -6944,103 +6944,103 @@
         <v>1.03</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG33" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH33" t="n">
         <v>1.09</v>
       </c>
       <c r="AI33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN33" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN33" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO33" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ33" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB33" t="n">
         <v>1.4</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD33" t="n">
         <v>2.62</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF33" t="n">
         <v>1.08</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G41" t="n">

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,38 +6707,38 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R32" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S32" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T32" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U32" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W32" t="n">
         <v>2.2</v>
       </c>
-      <c r="V32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X32" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z32" t="n">
         <v>8.9</v>
@@ -6747,103 +6747,103 @@
         <v>1.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG32" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH32" t="n">
         <v>1.09</v>
       </c>
       <c r="AI32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN32" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN32" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ32" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB32" t="n">
         <v>1.4</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD32" t="n">
         <v>2.62</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF32" t="n">
         <v>1.08</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46141.60416666666</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,38 +6904,38 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S33" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U33" t="n">
         <v>2.2</v>
       </c>
-      <c r="S33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U33" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V33" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W33" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X33" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z33" t="n">
         <v>8.9</v>
@@ -6944,103 +6944,103 @@
         <v>1.03</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG33" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH33" t="n">
         <v>1.09</v>
       </c>
       <c r="AI33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT33" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB33" t="n">
         <v>1.4</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD33" t="n">
         <v>2.62</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF33" t="n">
         <v>1.08</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI33" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G41" t="n">

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,38 +6707,38 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S32" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U32" t="n">
         <v>2.2</v>
       </c>
-      <c r="S32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V32" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W32" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X32" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z32" t="n">
         <v>8.9</v>
@@ -6747,103 +6747,103 @@
         <v>1.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG32" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH32" t="n">
         <v>1.09</v>
       </c>
       <c r="AI32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT32" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB32" t="n">
         <v>1.4</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD32" t="n">
         <v>2.62</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF32" t="n">
         <v>1.08</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46141.60416666666</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,38 +6904,38 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R33" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S33" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T33" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U33" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W33" t="n">
         <v>2.2</v>
       </c>
-      <c r="V33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X33" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z33" t="n">
         <v>8.9</v>
@@ -6944,103 +6944,103 @@
         <v>1.03</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG33" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH33" t="n">
         <v>1.09</v>
       </c>
       <c r="AI33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN33" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN33" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO33" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ33" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB33" t="n">
         <v>1.4</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD33" t="n">
         <v>2.62</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF33" t="n">
         <v>1.08</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G41" t="n">

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,38 +6707,38 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R32" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S32" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T32" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U32" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W32" t="n">
         <v>2.2</v>
       </c>
-      <c r="V32" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X32" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z32" t="n">
         <v>8.9</v>
@@ -6747,103 +6747,103 @@
         <v>1.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG32" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH32" t="n">
         <v>1.09</v>
       </c>
       <c r="AI32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN32" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN32" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS32" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ32" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB32" t="n">
         <v>1.4</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD32" t="n">
         <v>2.62</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF32" t="n">
         <v>1.08</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
         <v>46141.60416666666</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,38 +6904,38 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S33" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U33" t="n">
         <v>2.2</v>
       </c>
-      <c r="S33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U33" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V33" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W33" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X33" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z33" t="n">
         <v>8.9</v>
@@ -6944,103 +6944,103 @@
         <v>1.03</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG33" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH33" t="n">
         <v>1.09</v>
       </c>
       <c r="AI33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT33" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB33" t="n">
         <v>1.4</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD33" t="n">
         <v>2.62</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF33" t="n">
         <v>1.08</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI33" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G41" t="n">

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI44"/>
+  <dimension ref="A1:BI48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46141.5</v>
+        <v>46141.47916666666</v>
       </c>
     </row>
     <row r="15">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46141.5</v>
+        <v>46141.47916666666</v>
       </c>
     </row>
     <row r="16">
@@ -3506,27 +3506,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46141.5</v>
+        <v>46141.47916666666</v>
       </c>
     </row>
     <row r="17">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46141.51388888889</v>
+        <v>46141.47916666666</v>
       </c>
     </row>
     <row r="18">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46141.54166666666</v>
+        <v>46141.5</v>
       </c>
     </row>
     <row r="19">
@@ -4097,27 +4097,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46141.54166666666</v>
+        <v>46141.5</v>
       </c>
     </row>
     <row r="20">
@@ -4294,27 +4294,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46141.54166666666</v>
+        <v>46141.5</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46141.54166666666</v>
+        <v>46141.51388888889</v>
       </c>
     </row>
     <row r="22">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46141.54861111111</v>
+        <v>46141.54166666666</v>
       </c>
     </row>
     <row r="25">
@@ -5279,27 +5279,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46141.5625</v>
+        <v>46141.54166666666</v>
       </c>
     </row>
     <row r="26">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46141.57291666666</v>
+        <v>46141.54166666666</v>
       </c>
     </row>
     <row r="27">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46141.58333333334</v>
+        <v>46141.54166666666</v>
       </c>
     </row>
     <row r="28">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46141.58333333334</v>
+        <v>46141.54861111111</v>
       </c>
     </row>
     <row r="29">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46141.58333333334</v>
+        <v>46141.5625</v>
       </c>
     </row>
     <row r="30">
@@ -6264,12 +6264,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46141.58333333334</v>
+        <v>46141.57291666666</v>
       </c>
     </row>
     <row r="31">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6658,27 +6658,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6707,137 +6707,137 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3.55</v>
+        <v>2.06</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.9</v>
+        <v>3.67</v>
       </c>
       <c r="R32" t="n">
-        <v>2.2</v>
+        <v>3.46</v>
       </c>
       <c r="S32" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46141.60416666666</v>
+        <v>46141.58333333334</v>
       </c>
     </row>
     <row r="33">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,142 +6908,142 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46141.60416666666</v>
+        <v>46141.58333333334</v>
       </c>
     </row>
     <row r="34">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
-        <v>46141.625</v>
+        <v>46141.58333333334</v>
       </c>
     </row>
     <row r="35">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46141.625</v>
+        <v>46141.58333333334</v>
       </c>
     </row>
     <row r="36">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,137 +7495,137 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
-        <v>46141.66666666666</v>
+        <v>46141.60416666666</v>
       </c>
     </row>
     <row r="37">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,142 +7696,142 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46141.66666666666</v>
+        <v>46141.60416666666</v>
       </c>
     </row>
     <row r="38">
@@ -7840,12 +7840,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,79 +7893,79 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.11</v>
+        <v>1.02</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.39</v>
+        <v>10.2</v>
       </c>
       <c r="R38" t="n">
-        <v>2.51</v>
+        <v>28</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.96</v>
+        <v>1.3</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.75</v>
+        <v>3.4</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -8007,19 +8007,19 @@
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46141.66666666666</v>
+        <v>46141.625</v>
       </c>
     </row>
     <row r="39">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,112 +8090,112 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
         <v>0</v>
@@ -8204,19 +8204,19 @@
         <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46141.67708333334</v>
+        <v>46141.625</v>
       </c>
     </row>
     <row r="40">
@@ -8234,27 +8234,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46141.83333333334</v>
+        <v>46141.66666666666</v>
       </c>
     </row>
     <row r="41">
@@ -8431,27 +8431,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
-        <v>46141.83333333334</v>
+        <v>46141.66666666666</v>
       </c>
     </row>
     <row r="42">
@@ -8628,27 +8628,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
-        <v>46141.875</v>
+        <v>46141.66666666666</v>
       </c>
     </row>
     <row r="43">
@@ -8825,27 +8825,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,112 +8878,112 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>1.12</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.4</v>
+        <v>8.5</v>
       </c>
       <c r="R43" t="n">
-        <v>3.1</v>
+        <v>21</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.78</v>
+        <v>1.41</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.99</v>
+        <v>2.54</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ43" t="n">
         <v>0</v>
@@ -8992,19 +8992,19 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9013,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="BI43" s="3" t="n">
-        <v>46141.91666666666</v>
+        <v>46141.67708333334</v>
       </c>
     </row>
     <row r="44">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9210,6 +9210,794 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3" t="n">
+        <v>46141.83333333334</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Boston Legacy W</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>North Carolina Courage</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI45" s="3" t="n">
+        <v>46141.83333333334</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Chicago Red Stars</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gotham FC</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI46" s="3" t="n">
+        <v>46141.875</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tulsa Roughnecks</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R47" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI47" s="3" t="n">
+        <v>46141.91666666666</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Portland Thorns</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>San Diego Wave</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI48" s="3" t="n">
         <v>46141.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,38 +7495,38 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S36" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U36" t="n">
         <v>2.2</v>
       </c>
-      <c r="S36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U36" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V36" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W36" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X36" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z36" t="n">
         <v>8.9</v>
@@ -7535,103 +7535,103 @@
         <v>1.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG36" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH36" t="n">
         <v>1.09</v>
       </c>
       <c r="AI36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT36" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB36" t="n">
         <v>1.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD36" t="n">
         <v>2.62</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF36" t="n">
         <v>1.08</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,38 +7692,38 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S37" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T37" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U37" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W37" t="n">
         <v>2.2</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X37" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z37" t="n">
         <v>8.9</v>
@@ -7732,103 +7732,103 @@
         <v>1.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG37" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH37" t="n">
         <v>1.09</v>
       </c>
       <c r="AI37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN37" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN37" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO37" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS37" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ37" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB37" t="n">
         <v>1.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD37" t="n">
         <v>2.62</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF37" t="n">
         <v>1.08</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,79 +7893,79 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -8007,19 +8007,19 @@
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,79 +8090,79 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8204,19 +8204,19 @@
         <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,79 +7893,79 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -8007,19 +8007,19 @@
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,79 +8090,79 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8204,19 +8204,19 @@
         <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.67</v>
+        <v>2.6</v>
       </c>
       <c r="R35" t="n">
-        <v>3.46</v>
+        <v>3.05</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,38 +7495,38 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R36" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S36" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T36" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U36" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W36" t="n">
         <v>2.2</v>
       </c>
-      <c r="V36" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X36" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z36" t="n">
         <v>8.9</v>
@@ -7535,103 +7535,103 @@
         <v>1.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG36" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH36" t="n">
         <v>1.09</v>
       </c>
       <c r="AI36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM36" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN36" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN36" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS36" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ36" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB36" t="n">
         <v>1.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD36" t="n">
         <v>2.62</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF36" t="n">
         <v>1.08</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,38 +7692,38 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S37" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U37" t="n">
         <v>2.2</v>
       </c>
-      <c r="S37" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U37" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V37" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W37" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X37" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z37" t="n">
         <v>8.9</v>
@@ -7732,103 +7732,103 @@
         <v>1.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG37" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH37" t="n">
         <v>1.09</v>
       </c>
       <c r="AI37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT37" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB37" t="n">
         <v>1.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD37" t="n">
         <v>2.62</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF37" t="n">
         <v>1.08</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46141.60416666666</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G45" t="n">

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.6</v>
+        <v>3.67</v>
       </c>
       <c r="R35" t="n">
-        <v>3.05</v>
+        <v>3.46</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,38 +7495,38 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S36" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U36" t="n">
         <v>2.2</v>
       </c>
-      <c r="S36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U36" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V36" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W36" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X36" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z36" t="n">
         <v>8.9</v>
@@ -7535,103 +7535,103 @@
         <v>1.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG36" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH36" t="n">
         <v>1.09</v>
       </c>
       <c r="AI36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT36" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB36" t="n">
         <v>1.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD36" t="n">
         <v>2.62</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF36" t="n">
         <v>1.08</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,38 +7692,38 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S37" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T37" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U37" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W37" t="n">
         <v>2.2</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X37" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z37" t="n">
         <v>8.9</v>
@@ -7732,103 +7732,103 @@
         <v>1.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG37" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH37" t="n">
         <v>1.09</v>
       </c>
       <c r="AI37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN37" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN37" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO37" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS37" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ37" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB37" t="n">
         <v>1.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD37" t="n">
         <v>2.62</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF37" t="n">
         <v>1.08</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,79 +7893,79 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -8007,19 +8007,19 @@
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,79 +8090,79 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8204,19 +8204,19 @@
         <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.6</v>
+        <v>3.67</v>
       </c>
       <c r="R33" t="n">
-        <v>3.05</v>
+        <v>3.46</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.67</v>
+        <v>2.6</v>
       </c>
       <c r="R35" t="n">
-        <v>3.46</v>
+        <v>3.05</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,79 +7893,79 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -8007,19 +8007,19 @@
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,79 +8090,79 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8204,19 +8204,19 @@
         <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G45" t="n">

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.67</v>
+        <v>2.6</v>
       </c>
       <c r="R33" t="n">
-        <v>3.46</v>
+        <v>3.05</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.6</v>
+        <v>3.67</v>
       </c>
       <c r="R35" t="n">
-        <v>3.05</v>
+        <v>3.46</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G45" t="n">

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.6</v>
+        <v>3.67</v>
       </c>
       <c r="R33" t="n">
-        <v>3.05</v>
+        <v>3.46</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,38 +7495,38 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R36" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S36" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T36" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U36" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W36" t="n">
         <v>2.2</v>
       </c>
-      <c r="V36" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X36" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z36" t="n">
         <v>8.9</v>
@@ -7535,103 +7535,103 @@
         <v>1.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG36" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH36" t="n">
         <v>1.09</v>
       </c>
       <c r="AI36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM36" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN36" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN36" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS36" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ36" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB36" t="n">
         <v>1.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD36" t="n">
         <v>2.62</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF36" t="n">
         <v>1.08</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,38 +7692,38 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S37" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U37" t="n">
         <v>2.2</v>
       </c>
-      <c r="S37" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U37" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V37" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W37" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X37" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z37" t="n">
         <v>8.9</v>
@@ -7732,103 +7732,103 @@
         <v>1.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG37" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH37" t="n">
         <v>1.09</v>
       </c>
       <c r="AI37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT37" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB37" t="n">
         <v>1.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD37" t="n">
         <v>2.62</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF37" t="n">
         <v>1.08</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,79 +7893,79 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -8007,19 +8007,19 @@
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,79 +8090,79 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8204,19 +8204,19 @@
         <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G42" t="n">

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.67</v>
+        <v>2.6</v>
       </c>
       <c r="R33" t="n">
-        <v>3.46</v>
+        <v>3.05</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,38 +7495,38 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S36" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U36" t="n">
         <v>2.2</v>
       </c>
-      <c r="S36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U36" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V36" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W36" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X36" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z36" t="n">
         <v>8.9</v>
@@ -7535,103 +7535,103 @@
         <v>1.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG36" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH36" t="n">
         <v>1.09</v>
       </c>
       <c r="AI36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT36" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB36" t="n">
         <v>1.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD36" t="n">
         <v>2.62</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF36" t="n">
         <v>1.08</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,38 +7692,38 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S37" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T37" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U37" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W37" t="n">
         <v>2.2</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X37" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z37" t="n">
         <v>8.9</v>
@@ -7732,103 +7732,103 @@
         <v>1.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG37" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH37" t="n">
         <v>1.09</v>
       </c>
       <c r="AI37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN37" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN37" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO37" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS37" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ37" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB37" t="n">
         <v>1.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD37" t="n">
         <v>2.62</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF37" t="n">
         <v>1.08</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,79 +7893,79 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -8007,19 +8007,19 @@
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,79 +8090,79 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8204,19 +8204,19 @@
         <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G45" t="n">

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,38 +7495,38 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R36" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S36" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T36" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U36" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W36" t="n">
         <v>2.2</v>
       </c>
-      <c r="V36" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X36" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z36" t="n">
         <v>8.9</v>
@@ -7535,103 +7535,103 @@
         <v>1.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG36" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH36" t="n">
         <v>1.09</v>
       </c>
       <c r="AI36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM36" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN36" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN36" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS36" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ36" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB36" t="n">
         <v>1.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD36" t="n">
         <v>2.62</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF36" t="n">
         <v>1.08</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,38 +7692,38 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S37" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U37" t="n">
         <v>2.2</v>
       </c>
-      <c r="S37" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U37" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V37" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W37" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X37" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z37" t="n">
         <v>8.9</v>
@@ -7732,103 +7732,103 @@
         <v>1.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG37" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH37" t="n">
         <v>1.09</v>
       </c>
       <c r="AI37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT37" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB37" t="n">
         <v>1.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD37" t="n">
         <v>2.62</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF37" t="n">
         <v>1.08</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46141.60416666666</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,38 +7495,38 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S36" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U36" t="n">
         <v>2.2</v>
       </c>
-      <c r="S36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U36" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V36" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W36" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X36" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z36" t="n">
         <v>8.9</v>
@@ -7535,103 +7535,103 @@
         <v>1.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG36" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH36" t="n">
         <v>1.09</v>
       </c>
       <c r="AI36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT36" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB36" t="n">
         <v>1.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD36" t="n">
         <v>2.62</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF36" t="n">
         <v>1.08</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,38 +7692,38 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S37" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T37" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U37" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W37" t="n">
         <v>2.2</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X37" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z37" t="n">
         <v>8.9</v>
@@ -7732,103 +7732,103 @@
         <v>1.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG37" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH37" t="n">
         <v>1.09</v>
       </c>
       <c r="AI37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN37" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN37" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO37" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS37" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ37" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB37" t="n">
         <v>1.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD37" t="n">
         <v>2.62</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF37" t="n">
         <v>1.08</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46141.60416666666</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="Q5" t="n">
         <v>3.3</v>
       </c>
       <c r="R5" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6523,124 +6523,124 @@
         <v>3.05</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,38 +7495,38 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R36" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S36" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T36" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U36" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W36" t="n">
         <v>2.2</v>
       </c>
-      <c r="V36" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X36" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z36" t="n">
         <v>8.9</v>
@@ -7535,103 +7535,103 @@
         <v>1.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG36" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH36" t="n">
         <v>1.09</v>
       </c>
       <c r="AI36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM36" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN36" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN36" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS36" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ36" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB36" t="n">
         <v>1.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD36" t="n">
         <v>2.62</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF36" t="n">
         <v>1.08</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,38 +7692,38 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R37" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S37" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U37" t="n">
         <v>2.2</v>
       </c>
-      <c r="S37" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U37" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V37" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W37" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X37" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z37" t="n">
         <v>8.9</v>
@@ -7732,103 +7732,103 @@
         <v>1.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG37" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH37" t="n">
         <v>1.09</v>
       </c>
       <c r="AI37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT37" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB37" t="n">
         <v>1.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD37" t="n">
         <v>2.62</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF37" t="n">
         <v>1.08</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46141.60416666666</v>
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.39</v>
+        <v>3.31</v>
       </c>
       <c r="R40" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.21</v>
+        <v>3.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.12</v>
+        <v>3.36</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="S2" t="n">
-        <v>2.84</v>
+        <v>3.66</v>
       </c>
       <c r="T2" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="U2" t="n">
-        <v>3.94</v>
+        <v>2.66</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>2.63</v>
+        <v>3.14</v>
       </c>
       <c r="X2" t="n">
-        <v>2.79</v>
+        <v>2.31</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AB2" t="n">
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.14</v>
+        <v>4.33</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.77</v>
+        <v>2.21</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.71</v>
+        <v>1.48</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.98</v>
+        <v>2.41</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.58</v>
+        <v>4.65</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.01</v>
+        <v>2.21</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.36</v>
+        <v>3.12</v>
       </c>
       <c r="R3" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="S3" t="n">
-        <v>3.66</v>
+        <v>2.84</v>
       </c>
       <c r="T3" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>2.66</v>
+        <v>3.94</v>
       </c>
       <c r="V3" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="X3" t="n">
-        <v>2.31</v>
+        <v>2.79</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
         <v>1.01</v>
       </c>
       <c r="AC3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BF3" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.24</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.67</v>
+        <v>2.71</v>
       </c>
       <c r="R32" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>6.98</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="R31" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="S31" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.71</v>
+        <v>3.67</v>
       </c>
       <c r="R32" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,38 +7495,38 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.55</v>
+        <v>7.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R36" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S36" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U36" t="n">
         <v>2.2</v>
       </c>
-      <c r="S36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U36" t="n">
-        <v>3.11</v>
-      </c>
       <c r="V36" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="W36" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X36" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z36" t="n">
         <v>8.9</v>
@@ -7535,103 +7535,103 @@
         <v>1.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG36" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AH36" t="n">
         <v>1.09</v>
       </c>
       <c r="AI36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="AT36" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="BB36" t="n">
         <v>1.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BD36" t="n">
         <v>2.62</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BF36" t="n">
         <v>1.08</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,38 +7692,38 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>7.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R37" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S37" t="n">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="T37" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="U37" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W37" t="n">
         <v>2.2</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X37" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z37" t="n">
         <v>8.9</v>
@@ -7732,103 +7732,103 @@
         <v>1.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG37" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AH37" t="n">
         <v>1.09</v>
       </c>
       <c r="AI37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AM37" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN37" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN37" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AO37" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AS37" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ37" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="BB37" t="n">
         <v>1.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD37" t="n">
         <v>2.62</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF37" t="n">
         <v>1.08</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,79 +7893,79 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -8007,19 +8007,19 @@
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,79 +8090,79 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8204,19 +8204,19 @@
         <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.01</v>
+        <v>2.21</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.36</v>
+        <v>3.12</v>
       </c>
       <c r="R2" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="S2" t="n">
-        <v>3.66</v>
+        <v>2.84</v>
       </c>
       <c r="T2" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
-        <v>2.66</v>
+        <v>3.94</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="X2" t="n">
-        <v>2.31</v>
+        <v>2.79</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AB2" t="n">
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BF2" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.24</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.21</v>
+        <v>3.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.12</v>
+        <v>3.36</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="S3" t="n">
-        <v>2.84</v>
+        <v>3.66</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="U3" t="n">
-        <v>3.94</v>
+        <v>2.66</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>2.63</v>
+        <v>3.14</v>
       </c>
       <c r="X3" t="n">
-        <v>2.79</v>
+        <v>2.31</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.1</v>
+        <v>5.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AB3" t="n">
         <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.14</v>
+        <v>4.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.77</v>
+        <v>2.21</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.25</v>
+        <v>4.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.71</v>
+        <v>1.48</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.98</v>
+        <v>2.41</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.58</v>
+        <v>4.65</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA12" t="n">
         <v>3</v>
       </c>
-      <c r="R12" t="n">
-        <v>4</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5541,34 +5541,34 @@
         <v>5.35</v>
       </c>
       <c r="T26" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="U26" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="V26" t="n">
         <v>1.2</v>
       </c>
       <c r="W26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X26" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AB26" t="n">
         <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AD26" t="n">
         <v>5.52</v>
@@ -5643,19 +5643,19 @@
         <v>1.3</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="BD26" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BE26" t="n">
         <v>2.12</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5932,13 +5932,13 @@
         <v>1.92</v>
       </c>
       <c r="S28" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="T28" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="U28" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="V28" t="n">
         <v>1.26</v>
@@ -5953,16 +5953,16 @@
         <v>1.48</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AB28" t="n">
         <v>1.03</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AD28" t="n">
         <v>4.2</v>
@@ -5974,7 +5974,7 @@
         <v>2.14</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="AH28" t="n">
         <v>1.45</v>
@@ -5983,7 +5983,7 @@
         <v>4.8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AK28" t="n">
         <v>1.57</v>
@@ -5992,7 +5992,7 @@
         <v>2.23</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.23</v>
+        <v>1.8</v>
       </c>
       <c r="AN28" t="n">
         <v>1.27</v>
@@ -6043,10 +6043,10 @@
         <v>1.9</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="BF28" t="n">
         <v>1.22</v>
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,22 +6514,22 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.71</v>
+        <v>3.64</v>
       </c>
       <c r="R31" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -6538,10 +6538,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -6553,40 +6553,40 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6595,49 +6595,49 @@
         <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU31" t="n">
         <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BB31" t="n">
         <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD31" t="n">
         <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7502,31 +7502,31 @@
         <v>7.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
         <v>1.49</v>
       </c>
       <c r="S36" t="n">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="T36" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="U36" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="V36" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="W36" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="X36" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z36" t="n">
         <v>8.9</v>
@@ -7538,67 +7538,67 @@
         <v>1.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AG36" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AI36" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.27</v>
+        <v>2.43</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AO36" t="n">
         <v>1.26</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AS36" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AX36" t="n">
         <v>1.3</v>
@@ -7607,22 +7607,22 @@
         <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BF36" t="n">
         <v>1.08</v>
@@ -7696,28 +7696,28 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.55</v>
+        <v>3.59</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="R37" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S37" t="n">
         <v>4.3</v>
       </c>
       <c r="T37" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="U37" t="n">
-        <v>3.11</v>
+        <v>3.02</v>
       </c>
       <c r="V37" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W37" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="X37" t="n">
         <v>3.6</v>
@@ -7732,13 +7732,13 @@
         <v>1.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AE37" t="n">
         <v>2.75</v>
@@ -7750,10 +7750,10 @@
         <v>5.3</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AI37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ37" t="n">
         <v>1.03</v>
@@ -7768,7 +7768,7 @@
         <v>1.37</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
@@ -7789,7 +7789,7 @@
         <v>4.28</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AV37" t="n">
         <v>1.96</v>
@@ -7798,13 +7798,13 @@
         <v>1.58</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AY37" t="n">
         <v>1.23</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="BA37" t="n">
         <v>1.62</v>
@@ -7816,10 +7816,10 @@
         <v>2.88</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="BF37" t="n">
         <v>1.08</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,79 +7893,79 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -8007,19 +8007,19 @@
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.02</v>
+        <v>1.9</v>
       </c>
       <c r="Q39" t="n">
-        <v>10.2</v>
+        <v>3.86</v>
       </c>
       <c r="R39" t="n">
-        <v>28</v>
+        <v>3.75</v>
       </c>
       <c r="S39" t="n">
-        <v>1.32</v>
+        <v>2.4</v>
       </c>
       <c r="T39" t="n">
-        <v>3.65</v>
+        <v>2.4</v>
       </c>
       <c r="U39" t="n">
-        <v>18.5</v>
+        <v>3.4</v>
       </c>
       <c r="V39" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="W39" t="n">
-        <v>4.75</v>
+        <v>3.34</v>
       </c>
       <c r="X39" t="n">
-        <v>1.77</v>
+        <v>2.24</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE39" t="n">
         <v>1.91</v>
       </c>
-      <c r="Z39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>2.5</v>
-      </c>
       <c r="BF39" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8881,49 +8881,49 @@
         <v>1.12</v>
       </c>
       <c r="Q43" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R43" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S43" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="T43" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="U43" t="n">
         <v>12.5</v>
       </c>
       <c r="V43" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="W43" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="X43" t="n">
         <v>2.16</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Z43" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA43" t="n">
         <v>1.15</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC43" t="n">
         <v>1.1</v>
       </c>
       <c r="AD43" t="n">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AF43" t="n">
         <v>2.54</v>
@@ -8932,22 +8932,22 @@
         <v>2.1</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AI43" t="n">
         <v>3.3</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK43" t="n">
         <v>2.38</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AN43" t="n">
         <v>6.1</v>
@@ -8992,7 +8992,7 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BC43" t="n">
         <v>1.61</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BD45" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9478,70 +9478,70 @@
         <v>1.41</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE46" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF46" t="n">
         <v>1.86</v>
       </c>
-      <c r="AF46" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9583,19 +9583,19 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q47" t="n">
         <v>3.4</v>
       </c>
       <c r="R47" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AF47" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC47" t="n">
         <v>1.99</v>
       </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>0</v>
-      </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.21</v>
+        <v>2.96</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="S2" t="n">
-        <v>2.84</v>
+        <v>3.63</v>
       </c>
       <c r="T2" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="U2" t="n">
-        <v>3.94</v>
+        <v>2.68</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>2.63</v>
+        <v>3.14</v>
       </c>
       <c r="X2" t="n">
-        <v>2.79</v>
+        <v>2.29</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AB2" t="n">
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.14</v>
+        <v>4.62</v>
       </c>
       <c r="AE2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="BE2" t="n">
         <v>1.92</v>
       </c>
-      <c r="AF2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.64</v>
-      </c>
       <c r="BF2" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.01</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>2.12</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>3.66</v>
+        <v>2.88</v>
       </c>
       <c r="T3" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>2.66</v>
+        <v>3.94</v>
       </c>
       <c r="V3" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="X3" t="n">
-        <v>2.31</v>
+        <v>2.79</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
         <v>1.01</v>
       </c>
       <c r="AC3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BF3" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.24</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1395,130 +1395,130 @@
         <v>3.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>4.05</v>
+        <v>3.88</v>
       </c>
       <c r="T5" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="U5" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="V5" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>2.71</v>
+        <v>2.92</v>
       </c>
       <c r="X5" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG5" t="n">
         <v>2.83</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.28</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.55</v>
+        <v>5.4</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AL5" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC5" t="n">
         <v>1.95</v>
       </c>
-      <c r="AM5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.11</v>
-      </c>
       <c r="BD5" t="n">
-        <v>3.74</v>
+        <v>4.15</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1616,10 +1616,10 @@
         <v>2.67</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA6" t="n">
         <v>1.05</v>
@@ -1637,22 +1637,22 @@
         <v>1.93</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.65</v>
+        <v>5.82</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL6" t="n">
         <v>2.05</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,22 +6514,22 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -6538,10 +6538,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -6553,40 +6553,40 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6595,49 +6595,49 @@
         <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
         <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
         <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
         <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,22 +6908,22 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -6932,10 +6932,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -6947,40 +6947,40 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -6989,49 +6989,49 @@
         <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU33" t="n">
         <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BB33" t="n">
         <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF33" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.02</v>
+        <v>1.9</v>
       </c>
       <c r="Q38" t="n">
-        <v>10.2</v>
+        <v>3.86</v>
       </c>
       <c r="R38" t="n">
-        <v>28</v>
+        <v>3.75</v>
       </c>
       <c r="S38" t="n">
-        <v>1.32</v>
+        <v>2.4</v>
       </c>
       <c r="T38" t="n">
-        <v>3.65</v>
+        <v>2.4</v>
       </c>
       <c r="U38" t="n">
-        <v>18.5</v>
+        <v>3.4</v>
       </c>
       <c r="V38" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="W38" t="n">
-        <v>4.75</v>
+        <v>3.34</v>
       </c>
       <c r="X38" t="n">
-        <v>1.77</v>
+        <v>2.24</v>
       </c>
       <c r="Y38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE38" t="n">
         <v>1.91</v>
       </c>
-      <c r="Z38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>2.5</v>
-      </c>
       <c r="BF38" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.86</v>
+        <v>12</v>
       </c>
       <c r="R39" t="n">
-        <v>3.75</v>
+        <v>29</v>
       </c>
       <c r="S39" t="n">
-        <v>2.4</v>
+        <v>1.31</v>
       </c>
       <c r="T39" t="n">
-        <v>2.4</v>
+        <v>3.65</v>
       </c>
       <c r="U39" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W39" t="n">
+        <v>5</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF39" t="n">
         <v>3.4</v>
       </c>
-      <c r="V39" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W39" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Y39" t="n">
+      <c r="AG39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z39" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK39" t="n">
-        <v>1.5</v>
+        <v>2.51</v>
       </c>
       <c r="AL39" t="n">
-        <v>2.75</v>
+        <v>1.44</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.83</v>
+        <v>7.6</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.91</v>
+        <v>2.66</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.96</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R2" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.63</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
-        <v>2.68</v>
+        <v>3.94</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="X2" t="n">
-        <v>2.29</v>
+        <v>2.79</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.25</v>
+        <v>7.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AB2" t="n">
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.62</v>
+        <v>3.14</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.21</v>
+        <v>1.77</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.48</v>
+        <v>1.71</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.65</v>
+        <v>3.58</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.2</v>
+        <v>2.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="S3" t="n">
-        <v>2.88</v>
+        <v>3.63</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="U3" t="n">
-        <v>3.94</v>
+        <v>2.68</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>2.63</v>
+        <v>3.14</v>
       </c>
       <c r="X3" t="n">
-        <v>2.79</v>
+        <v>2.29</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AB3" t="n">
         <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.14</v>
+        <v>4.62</v>
       </c>
       <c r="AE3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1.92</v>
       </c>
-      <c r="AF3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.68</v>
-      </c>
       <c r="BF3" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="R32" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="S32" t="n">
-        <v>3.12</v>
+        <v>3.64</v>
       </c>
       <c r="T32" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="U32" t="n">
-        <v>4.77</v>
+        <v>4.39</v>
       </c>
       <c r="V32" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="W32" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="X32" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z32" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AD32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AR32" t="n">
         <v>2.23</v>
       </c>
-      <c r="AE32" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AL32" t="n">
+      <c r="AS32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AW32" t="n">
         <v>1.57</v>
       </c>
-      <c r="AM32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AX32" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="BD32" t="n">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.64</v>
+        <v>2.7</v>
       </c>
       <c r="R33" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="S33" t="n">
-        <v>2.5</v>
+        <v>3.12</v>
       </c>
       <c r="T33" t="n">
-        <v>2.28</v>
+        <v>1.74</v>
       </c>
       <c r="U33" t="n">
-        <v>3.85</v>
+        <v>4.77</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X33" t="n">
-        <v>2.48</v>
+        <v>3.8</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.75</v>
+        <v>2.23</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.71</v>
+        <v>2.91</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.98</v>
+        <v>1.39</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.8</v>
+        <v>5.85</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="AI33" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.62</v>
+        <v>2.23</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="AS33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV33" t="n">
         <v>2.1</v>
       </c>
-      <c r="AT33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AW33" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.94</v>
+        <v>2.78</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,22 +7302,22 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -7326,10 +7326,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -7341,40 +7341,40 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7383,49 +7383,49 @@
         <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU35" t="n">
         <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BB35" t="n">
         <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD35" t="n">
         <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF35" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.86</v>
+        <v>12</v>
       </c>
       <c r="R38" t="n">
-        <v>3.75</v>
+        <v>29</v>
       </c>
       <c r="S38" t="n">
-        <v>2.4</v>
+        <v>1.31</v>
       </c>
       <c r="T38" t="n">
-        <v>2.4</v>
+        <v>3.65</v>
       </c>
       <c r="U38" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W38" t="n">
+        <v>5</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF38" t="n">
         <v>3.4</v>
       </c>
-      <c r="V38" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W38" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Y38" t="n">
+      <c r="AG38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z38" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK38" t="n">
-        <v>1.5</v>
+        <v>2.51</v>
       </c>
       <c r="AL38" t="n">
-        <v>2.75</v>
+        <v>1.44</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.83</v>
+        <v>7.6</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.91</v>
+        <v>2.66</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="Q39" t="n">
-        <v>12</v>
+        <v>3.86</v>
       </c>
       <c r="R39" t="n">
-        <v>29</v>
+        <v>3.75</v>
       </c>
       <c r="S39" t="n">
-        <v>1.31</v>
+        <v>2.4</v>
       </c>
       <c r="T39" t="n">
-        <v>3.65</v>
+        <v>2.4</v>
       </c>
       <c r="U39" t="n">
-        <v>17.73</v>
+        <v>3.4</v>
       </c>
       <c r="V39" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="W39" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z39" t="n">
         <v>5</v>
       </c>
-      <c r="X39" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Z39" t="n">
+      <c r="AA39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BA39" t="n">
         <v>3.1</v>
       </c>
-      <c r="AA39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>0</v>
-      </c>
       <c r="BB39" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="BD39" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.66</v>
+        <v>1.91</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>6.57</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="S2" t="n">
-        <v>2.88</v>
+        <v>3.96</v>
       </c>
       <c r="T2" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="U2" t="n">
-        <v>3.94</v>
+        <v>2.51</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>2.63</v>
+        <v>3.14</v>
       </c>
       <c r="X2" t="n">
-        <v>2.79</v>
+        <v>2.29</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AB2" t="n">
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.14</v>
+        <v>4.4</v>
       </c>
       <c r="AE2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE2" t="n">
         <v>1.92</v>
       </c>
-      <c r="AF2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.68</v>
-      </c>
       <c r="BF2" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.96</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>1.95</v>
+        <v>3.05</v>
       </c>
       <c r="S3" t="n">
-        <v>3.63</v>
+        <v>2.84</v>
       </c>
       <c r="T3" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>2.68</v>
+        <v>3.94</v>
       </c>
       <c r="V3" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="X3" t="n">
-        <v>2.29</v>
+        <v>2.79</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.25</v>
+        <v>7.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
         <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.62</v>
+        <v>3.14</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.21</v>
+        <v>1.77</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AI3" t="n">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.18</v>
+        <v>1.06</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.48</v>
+        <v>1.71</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.65</v>
+        <v>3.58</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1401,13 +1401,13 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="T5" t="n">
         <v>2.11</v>
       </c>
       <c r="U5" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="V5" t="n">
         <v>1.32</v>
@@ -1422,22 +1422,22 @@
         <v>1.41</v>
       </c>
       <c r="Z5" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AB5" t="n">
         <v>1.04</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AF5" t="n">
         <v>2.01</v>
@@ -1449,19 +1449,19 @@
         <v>1.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.4</v>
+        <v>5.42</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN5" t="n">
         <v>1.24</v>
@@ -1518,7 +1518,7 @@
         <v>1.74</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1613,7 +1613,7 @@
         <v>2.73</v>
       </c>
       <c r="X6" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="Y6" t="n">
         <v>1.39</v>
@@ -1637,13 +1637,13 @@
         <v>1.93</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AG6" t="n">
         <v>3.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AI6" t="n">
         <v>5.82</v>
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BC6" t="n">
         <v>2.05</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>5.53</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>5.53</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="R33" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="S33" t="n">
-        <v>3.12</v>
+        <v>3.64</v>
       </c>
       <c r="T33" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="U33" t="n">
-        <v>4.77</v>
+        <v>4.39</v>
       </c>
       <c r="V33" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="W33" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="X33" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="Z33" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AD33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AR33" t="n">
         <v>2.23</v>
       </c>
-      <c r="AE33" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AL33" t="n">
+      <c r="AS33" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AW33" t="n">
         <v>1.57</v>
       </c>
-      <c r="AM33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AX33" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="BD33" t="n">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
         <v>12</v>
       </c>
       <c r="R38" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S38" t="n">
         <v>1.31</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="R2" t="n">
-        <v>1.95</v>
+        <v>3.05</v>
       </c>
       <c r="S2" t="n">
-        <v>3.96</v>
+        <v>2.84</v>
       </c>
       <c r="T2" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
-        <v>2.51</v>
+        <v>3.94</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="W2" t="n">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="X2" t="n">
-        <v>2.29</v>
+        <v>2.79</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.25</v>
+        <v>7.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AB2" t="n">
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BF2" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>1.25</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>3.05</v>
+        <v>1.95</v>
       </c>
       <c r="S3" t="n">
-        <v>2.84</v>
+        <v>3.96</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>3.94</v>
+        <v>2.51</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>2.63</v>
+        <v>3.14</v>
       </c>
       <c r="X3" t="n">
-        <v>2.79</v>
+        <v>2.29</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AB3" t="n">
         <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.14</v>
+        <v>4.4</v>
       </c>
       <c r="AE3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1.92</v>
       </c>
-      <c r="AF3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.64</v>
-      </c>
       <c r="BF3" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2574,28 +2574,28 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="R11" t="n">
-        <v>4.24</v>
+        <v>4.29</v>
       </c>
       <c r="S11" t="n">
-        <v>2.55</v>
+        <v>2.77</v>
       </c>
       <c r="T11" t="n">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="U11" t="n">
-        <v>5.53</v>
+        <v>5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W11" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="X11" t="n">
         <v>3.6</v>
@@ -2610,22 +2610,22 @@
         <v>1.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AE11" t="n">
         <v>2.87</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>5.67</v>
+        <v>5.1</v>
       </c>
       <c r="AH11" t="n">
         <v>1.12</v>
@@ -2646,7 +2646,7 @@
         <v>1.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="BC11" t="n">
         <v>2.82</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="BE11" t="n">
         <v>1.35</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6129,16 +6129,16 @@
         <v>2.37</v>
       </c>
       <c r="S29" t="n">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="T29" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="U29" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="V29" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W29" t="n">
         <v>3.25</v>
@@ -6153,7 +6153,7 @@
         <v>5.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AB29" t="n">
         <v>1.03</v>
@@ -6165,13 +6165,13 @@
         <v>3.92</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.76</v>
+        <v>2.23</v>
       </c>
       <c r="AH29" t="n">
         <v>1.36</v>
@@ -6186,7 +6186,7 @@
         <v>1.57</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AM29" t="n">
         <v>1.25</v>
@@ -6237,13 +6237,13 @@
         <v>1.16</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BD29" t="n">
         <v>4.25</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="BF29" t="n">
         <v>1.19</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,22 +6711,22 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6735,10 +6735,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -6750,40 +6750,40 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6792,49 +6792,49 @@
         <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU32" t="n">
         <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BB32" t="n">
         <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="R33" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="S33" t="n">
-        <v>3.64</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="U33" t="n">
-        <v>4.39</v>
+        <v>4.77</v>
       </c>
       <c r="V33" t="n">
         <v>1.66</v>
       </c>
       <c r="W33" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="X33" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="Y33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1.14</v>
       </c>
-      <c r="Z33" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AC33" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="AE33" t="n">
-        <v>3.5</v>
+        <v>2.91</v>
       </c>
       <c r="AF33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY33" t="n">
         <v>1.26</v>
       </c>
-      <c r="AG33" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AH33" t="n">
+      <c r="AZ33" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BF33" t="n">
         <v>1.05</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>1.02</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.64</v>
+        <v>2.6</v>
       </c>
       <c r="R35" t="n">
-        <v>3.44</v>
+        <v>3.05</v>
       </c>
       <c r="S35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
         <v>2.5</v>
       </c>
-      <c r="T35" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U35" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
       <c r="AV35" t="n">
-        <v>2.55</v>
+        <v>1.92</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.94</v>
+        <v>3.18</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,143 +7495,143 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>7.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="R36" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="T36" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="U36" t="n">
-        <v>2.09</v>
+        <v>3</v>
       </c>
       <c r="V36" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="W36" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="X36" t="n">
-        <v>3.58</v>
+        <v>4.15</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>8.9</v>
+        <v>15</v>
       </c>
       <c r="AA36" t="n">
         <v>1.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.52</v>
+        <v>2.97</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AG36" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AI36" t="n">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.98</v>
+        <v>2.4</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AM36" t="n">
-        <v>2.43</v>
+        <v>1.44</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AO36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="AS36" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AX36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BE36" t="n">
         <v>1.3</v>
       </c>
-      <c r="AY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>1.39</v>
-      </c>
       <c r="BF36" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,38 +7692,38 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.59</v>
+        <v>7.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="R37" t="n">
-        <v>2.22</v>
+        <v>1.49</v>
       </c>
       <c r="S37" t="n">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="T37" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="U37" t="n">
-        <v>3.02</v>
+        <v>2.09</v>
       </c>
       <c r="V37" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W37" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="X37" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z37" t="n">
         <v>8.9</v>
@@ -7732,103 +7732,103 @@
         <v>1.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.75</v>
+        <v>2.52</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AG37" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AI37" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.32</v>
+        <v>2.98</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="AM37" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BB37" t="n">
         <v>1.37</v>
       </c>
-      <c r="AN37" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BC37" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="BD37" t="n">
         <v>2.75</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="BF37" t="n">
         <v>1.08</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="Q38" t="n">
-        <v>12</v>
+        <v>3.86</v>
       </c>
       <c r="R38" t="n">
-        <v>23</v>
+        <v>3.75</v>
       </c>
       <c r="S38" t="n">
-        <v>1.31</v>
+        <v>2.4</v>
       </c>
       <c r="T38" t="n">
-        <v>3.65</v>
+        <v>2.4</v>
       </c>
       <c r="U38" t="n">
-        <v>17.73</v>
+        <v>3.4</v>
       </c>
       <c r="V38" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="W38" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z38" t="n">
         <v>5</v>
       </c>
-      <c r="X38" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Z38" t="n">
+      <c r="AA38" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BA38" t="n">
         <v>3.1</v>
       </c>
-      <c r="AA38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>0</v>
-      </c>
       <c r="BB38" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="BD38" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.66</v>
+        <v>1.91</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.86</v>
+        <v>12</v>
       </c>
       <c r="R39" t="n">
-        <v>3.75</v>
+        <v>23</v>
       </c>
       <c r="S39" t="n">
-        <v>2.4</v>
+        <v>1.31</v>
       </c>
       <c r="T39" t="n">
-        <v>2.4</v>
+        <v>3.65</v>
       </c>
       <c r="U39" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W39" t="n">
+        <v>5</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF39" t="n">
         <v>3.4</v>
       </c>
-      <c r="V39" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W39" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Y39" t="n">
+      <c r="AG39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z39" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK39" t="n">
-        <v>1.5</v>
+        <v>2.51</v>
       </c>
       <c r="AL39" t="n">
-        <v>2.75</v>
+        <v>1.44</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.83</v>
+        <v>7.6</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.75</v>
+        <v>1.39</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.91</v>
+        <v>2.66</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Q43" t="n">
-        <v>8.300000000000001</v>
+        <v>12</v>
       </c>
       <c r="R43" t="n">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="S43" t="n">
         <v>1.44</v>
@@ -8893,7 +8893,7 @@
         <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="V43" t="n">
         <v>1.2</v>
@@ -8905,10 +8905,10 @@
         <v>2.16</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA43" t="n">
         <v>1.15</v>
@@ -8926,7 +8926,7 @@
         <v>1.45</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="AG43" t="n">
         <v>2.1</v>
@@ -8941,13 +8941,13 @@
         <v>1.28</v>
       </c>
       <c r="AK43" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AL43" t="n">
         <v>1.56</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AN43" t="n">
         <v>6.1</v>
@@ -8992,19 +8992,19 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="BE43" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>6.57</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD45" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9478,13 +9478,13 @@
         <v>1.41</v>
       </c>
       <c r="S46" t="n">
-        <v>7.19</v>
+        <v>6.8</v>
       </c>
       <c r="T46" t="n">
         <v>2.26</v>
       </c>
       <c r="U46" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="V46" t="n">
         <v>1.32</v>
@@ -9508,13 +9508,13 @@
         <v>1</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AD46" t="n">
         <v>3.42</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AF46" t="n">
         <v>1.86</v>
@@ -9526,16 +9526,16 @@
         <v>1.28</v>
       </c>
       <c r="AI46" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AJ46" t="n">
         <v>1.09</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AM46" t="n">
         <v>1.14</v>
@@ -9675,19 +9675,19 @@
         <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="T47" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="U47" t="n">
         <v>3.64</v>
       </c>
       <c r="V47" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W47" t="n">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="X47" t="n">
         <v>2.53</v>
@@ -9711,34 +9711,34 @@
         <v>3.58</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.83</v>
+        <v>2.94</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AI47" t="n">
         <v>5.39</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL47" t="n">
         <v>2.15</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9783,7 +9783,7 @@
         <v>1.17</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="BD47" t="n">
         <v>3.96</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R2" t="n">
-        <v>3.05</v>
+        <v>1.91</v>
       </c>
       <c r="S2" t="n">
-        <v>2.84</v>
+        <v>3.96</v>
       </c>
       <c r="T2" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="U2" t="n">
-        <v>3.94</v>
+        <v>2.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>2.63</v>
+        <v>3.14</v>
       </c>
       <c r="X2" t="n">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AB2" t="n">
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN2" t="n">
         <v>1.27</v>
       </c>
-      <c r="AD2" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE2" t="n">
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE2" t="n">
         <v>1.92</v>
       </c>
-      <c r="AF2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.64</v>
-      </c>
       <c r="BF2" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,80 +998,80 @@
         </is>
       </c>
       <c r="P3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S3" t="n">
         <v>3</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.96</v>
-      </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>2.51</v>
+        <v>3.64</v>
       </c>
       <c r="V3" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="X3" t="n">
-        <v>2.29</v>
+        <v>2.79</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>5.25</v>
+        <v>7.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
         <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.4</v>
+        <v>3.14</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.53</v>
+        <v>1.92</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.23</v>
+        <v>1.77</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.33</v>
+        <v>2.88</v>
       </c>
       <c r="AH3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN3" t="n">
         <v>1.47</v>
       </c>
-      <c r="AI3" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.7</v>
+        <v>3.58</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1401,10 +1401,10 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>3.92</v>
+        <v>3.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
         <v>2.53</v>
@@ -1413,13 +1413,13 @@
         <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>2.92</v>
+        <v>3.18</v>
       </c>
       <c r="X5" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="Z5" t="n">
         <v>6.5</v>
@@ -1428,19 +1428,19 @@
         <v>1.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AD5" t="n">
         <v>3.72</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AG5" t="n">
         <v>2.83</v>
@@ -1449,7 +1449,7 @@
         <v>1.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.42</v>
+        <v>5.45</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.08</v>
@@ -1458,13 +1458,13 @@
         <v>1.62</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AM5" t="n">
         <v>1.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1598,13 +1598,13 @@
         <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="T6" t="n">
         <v>2.05</v>
       </c>
       <c r="U6" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="V6" t="n">
         <v>1.36</v>
@@ -1613,13 +1613,13 @@
         <v>2.73</v>
       </c>
       <c r="X6" t="n">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AA6" t="n">
         <v>1.05</v>
@@ -1640,28 +1640,28 @@
         <v>1.89</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="AH6" t="n">
         <v>1.28</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.82</v>
+        <v>5.99</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AL6" t="n">
         <v>2.05</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BC6" t="n">
         <v>2.05</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5923,61 +5923,61 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="Q28" t="n">
         <v>3.7</v>
       </c>
       <c r="R28" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="S28" t="n">
-        <v>3.82</v>
+        <v>3.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="U28" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="V28" t="n">
         <v>1.26</v>
       </c>
       <c r="W28" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="X28" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="Y28" t="n">
         <v>1.48</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB28" t="n">
         <v>1.03</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.2</v>
+        <v>4.12</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AG28" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AI28" t="n">
         <v>4.8</v>
@@ -5992,7 +5992,7 @@
         <v>2.23</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.8</v>
+        <v>1.23</v>
       </c>
       <c r="AN28" t="n">
         <v>1.27</v>
@@ -6037,7 +6037,7 @@
         <v>1.56</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BC28" t="n">
         <v>1.9</v>
@@ -6049,7 +6049,7 @@
         <v>1.8</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.86</v>
+        <v>10.2</v>
       </c>
       <c r="R38" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T38" t="n">
         <v>3.75</v>
       </c>
-      <c r="S38" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.4</v>
-      </c>
       <c r="U38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W38" t="n">
+        <v>5</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF38" t="n">
         <v>3.4</v>
       </c>
-      <c r="V38" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W38" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB38" t="n">
+      <c r="AG38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AZ38" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC38" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK38" t="n">
+      <c r="BA38" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC38" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BD38" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="Q39" t="n">
-        <v>12</v>
+        <v>3.9</v>
       </c>
       <c r="R39" t="n">
-        <v>23</v>
+        <v>3.6</v>
       </c>
       <c r="S39" t="n">
-        <v>1.31</v>
+        <v>2.5</v>
       </c>
       <c r="T39" t="n">
-        <v>3.65</v>
+        <v>2.34</v>
       </c>
       <c r="U39" t="n">
-        <v>17.73</v>
+        <v>4</v>
       </c>
       <c r="V39" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="W39" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z39" t="n">
         <v>5</v>
       </c>
-      <c r="X39" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Z39" t="n">
+      <c r="AA39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BA39" t="n">
         <v>3.1</v>
       </c>
-      <c r="AA39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>0</v>
-      </c>
       <c r="BB39" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="BD39" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.66</v>
+        <v>1.91</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,80 +801,80 @@
         </is>
       </c>
       <c r="P2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q2" t="n">
         <v>3.25</v>
       </c>
-      <c r="Q2" t="n">
-        <v>3.6</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="S2" t="n">
-        <v>3.96</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
-        <v>2.4</v>
+        <v>3.64</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="X2" t="n">
-        <v>2.38</v>
+        <v>2.79</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AB2" t="n">
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.4</v>
+        <v>3.14</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.23</v>
+        <v>1.77</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AH2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN2" t="n">
         <v>1.47</v>
       </c>
-      <c r="AI2" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.7</v>
+        <v>3.58</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>3.96</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>3.64</v>
+        <v>2.4</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="X3" t="n">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AB3" t="n">
         <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.14</v>
+        <v>4.4</v>
       </c>
       <c r="AE3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE3" t="n">
         <v>1.92</v>
       </c>
-      <c r="AF3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.64</v>
-      </c>
       <c r="BF3" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,22 +6514,22 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -6538,10 +6538,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -6553,40 +6553,40 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6595,49 +6595,49 @@
         <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU31" t="n">
         <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BB31" t="n">
         <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD31" t="n">
         <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,22 +6711,22 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6735,10 +6735,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -6750,40 +6750,40 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6792,49 +6792,49 @@
         <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
         <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
         <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,130 +7105,130 @@
         </is>
       </c>
       <c r="P34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="X34" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="BD34" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q34" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="R34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U34" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="W34" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>2.66</v>
-      </c>
       <c r="BE34" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="BF34" t="n">
         <v>1.05</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,130 +7302,130 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q35" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS35" t="n">
         <v>2.6</v>
       </c>
-      <c r="R35" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="S35" t="n">
+      <c r="AT35" t="n">
         <v>3.4</v>
       </c>
-      <c r="T35" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="X35" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK35" t="n">
+      <c r="AU35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BA35" t="n">
         <v>2.45</v>
       </c>
-      <c r="AL35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>2.15</v>
-      </c>
       <c r="BB35" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="BC35" t="n">
-        <v>3.18</v>
+        <v>2.78</v>
       </c>
       <c r="BD35" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="BF35" t="n">
         <v>1.05</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,143 +7495,143 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.7</v>
+        <v>6.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="R36" t="n">
-        <v>2.2</v>
+        <v>1.49</v>
       </c>
       <c r="S36" t="n">
-        <v>4.6</v>
+        <v>6.9</v>
       </c>
       <c r="T36" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="U36" t="n">
-        <v>3</v>
+        <v>2.06</v>
       </c>
       <c r="V36" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="W36" t="n">
-        <v>2.15</v>
+        <v>2.47</v>
       </c>
       <c r="X36" t="n">
-        <v>4.15</v>
+        <v>3.18</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z36" t="n">
-        <v>15</v>
+        <v>7.9</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.08</v>
+        <v>2.59</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.97</v>
+        <v>2.27</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AI36" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK36" t="n">
         <v>2.4</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AT36" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="BC36" t="n">
-        <v>3.2</v>
+        <v>2.44</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,143 +7692,143 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>7.75</v>
+        <v>3.59</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="R37" t="n">
-        <v>1.49</v>
+        <v>2.22</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="T37" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="U37" t="n">
-        <v>2.09</v>
+        <v>3</v>
       </c>
       <c r="V37" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="W37" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="X37" t="n">
-        <v>3.58</v>
+        <v>4.15</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>8.9</v>
+        <v>15</v>
       </c>
       <c r="AA37" t="n">
         <v>1.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.52</v>
+        <v>2.97</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AG37" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AI37" t="n">
-        <v>9.300000000000001</v>
+        <v>11</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.98</v>
+        <v>2.4</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AM37" t="n">
-        <v>2.43</v>
+        <v>1.44</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AO37" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="AS37" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AX37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BE37" t="n">
         <v>1.3</v>
       </c>
-      <c r="AY37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.39</v>
-      </c>
       <c r="BF37" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46141.60416666666</v>
@@ -8484,19 +8484,19 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="R41" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="S41" t="n">
         <v>3.4</v>
       </c>
       <c r="T41" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
         <v>3.2</v>
@@ -8508,10 +8508,10 @@
         <v>2.67</v>
       </c>
       <c r="X41" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z41" t="n">
         <v>8.9</v>
@@ -8520,22 +8520,22 @@
         <v>1.03</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG41" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AH41" t="n">
         <v>1.22</v>
@@ -8547,16 +8547,16 @@
         <v>1.06</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8568,10 +8568,10 @@
         <v>1.52</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AT41" t="n">
         <v>3.1</v>
@@ -8583,16 +8583,16 @@
         <v>2.33</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AY41" t="n">
         <v>1.32</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="BA41" t="n">
         <v>2.1</v>
@@ -8601,16 +8601,16 @@
         <v>1.3</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8893,7 +8893,7 @@
         <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="V43" t="n">
         <v>1.2</v>
@@ -8926,7 +8926,7 @@
         <v>1.45</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AG43" t="n">
         <v>2.1</v>
@@ -8941,13 +8941,13 @@
         <v>1.28</v>
       </c>
       <c r="AK43" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AL43" t="n">
         <v>1.56</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AN43" t="n">
         <v>6.1</v>
@@ -8992,7 +8992,7 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BC43" t="n">
         <v>1.65</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R2" t="n">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>3.96</v>
       </c>
       <c r="T2" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="U2" t="n">
-        <v>3.64</v>
+        <v>2.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="X2" t="n">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AB2" t="n">
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.14</v>
+        <v>4.4</v>
       </c>
       <c r="AE2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE2" t="n">
         <v>1.92</v>
       </c>
-      <c r="AF2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.64</v>
-      </c>
       <c r="BF2" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,80 +998,80 @@
         </is>
       </c>
       <c r="P3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3.25</v>
       </c>
-      <c r="Q3" t="n">
-        <v>3.6</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.91</v>
+        <v>2.88</v>
       </c>
       <c r="S3" t="n">
-        <v>3.96</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4</v>
+        <v>3.64</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="X3" t="n">
-        <v>2.38</v>
+        <v>2.79</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
         <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.4</v>
+        <v>3.14</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.57</v>
+        <v>1.92</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.23</v>
+        <v>1.77</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AH3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN3" t="n">
         <v>1.47</v>
       </c>
-      <c r="AI3" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.7</v>
+        <v>3.58</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,22 +6514,22 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -6538,10 +6538,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -6553,40 +6553,40 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6595,49 +6595,49 @@
         <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
         <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
         <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
         <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,22 +6711,22 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6735,10 +6735,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -6750,40 +6750,40 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6792,49 +6792,49 @@
         <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU32" t="n">
         <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BB32" t="n">
         <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,130 +7105,130 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q34" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS34" t="n">
         <v>2.6</v>
       </c>
-      <c r="R34" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="S34" t="n">
+      <c r="AT34" t="n">
         <v>3.4</v>
       </c>
-      <c r="T34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U34" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="X34" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK34" t="n">
+      <c r="AU34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BA34" t="n">
         <v>2.45</v>
       </c>
-      <c r="AL34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>2.15</v>
-      </c>
       <c r="BB34" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="BC34" t="n">
-        <v>3.18</v>
+        <v>2.78</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="BF34" t="n">
         <v>1.05</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,130 +7302,130 @@
         </is>
       </c>
       <c r="P35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R35" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="X35" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="BD35" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q35" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="R35" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U35" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="W35" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>2.66</v>
-      </c>
       <c r="BE35" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="BF35" t="n">
         <v>1.05</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="Q38" t="n">
-        <v>10.2</v>
+        <v>3.9</v>
       </c>
       <c r="R38" t="n">
-        <v>17.11</v>
+        <v>3.6</v>
       </c>
       <c r="S38" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="T38" t="n">
-        <v>3.75</v>
+        <v>2.34</v>
       </c>
       <c r="U38" t="n">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="V38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W38" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC38" t="n">
         <v>1.15</v>
       </c>
-      <c r="W38" t="n">
-        <v>5</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA38" t="n">
+      <c r="AD38" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY38" t="n">
         <v>1.3</v>
       </c>
-      <c r="AB38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AZ38" t="n">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="BA38" t="n">
-        <v>14</v>
+        <v>3.1</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="BD38" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.91</v>
+        <v>1.04</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.9</v>
+        <v>10.2</v>
       </c>
       <c r="R39" t="n">
-        <v>3.6</v>
+        <v>17.11</v>
       </c>
       <c r="S39" t="n">
-        <v>2.5</v>
+        <v>1.33</v>
       </c>
       <c r="T39" t="n">
-        <v>2.34</v>
+        <v>3.75</v>
       </c>
       <c r="U39" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="V39" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="W39" t="n">
-        <v>3.34</v>
+        <v>5</v>
       </c>
       <c r="X39" t="n">
-        <v>2.24</v>
+        <v>1.77</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.57</v>
+        <v>1.99</v>
       </c>
       <c r="Z39" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AZ39" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC39" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK39" t="n">
+      <c r="BA39" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC39" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BD39" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9478,25 +9478,25 @@
         <v>1.41</v>
       </c>
       <c r="S46" t="n">
-        <v>6.8</v>
+        <v>7.19</v>
       </c>
       <c r="T46" t="n">
         <v>2.26</v>
       </c>
       <c r="U46" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="V46" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W46" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="X46" t="n">
         <v>2.67</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z46" t="n">
         <v>6.4</v>
@@ -9517,7 +9517,7 @@
         <v>1.83</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AG46" t="n">
         <v>3.08</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,22 +6711,22 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6735,10 +6735,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -6750,40 +6750,40 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6792,49 +6792,49 @@
         <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
         <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
         <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,22 +6908,22 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -6932,10 +6932,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -6947,40 +6947,40 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -6989,49 +6989,49 @@
         <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU33" t="n">
         <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BB33" t="n">
         <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,130 +7302,130 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q35" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS35" t="n">
         <v>2.6</v>
       </c>
-      <c r="R35" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="S35" t="n">
+      <c r="AT35" t="n">
         <v>3.4</v>
       </c>
-      <c r="T35" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="X35" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK35" t="n">
+      <c r="AU35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BA35" t="n">
         <v>2.45</v>
       </c>
-      <c r="AL35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>2.15</v>
-      </c>
       <c r="BB35" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="BC35" t="n">
-        <v>3.18</v>
+        <v>2.78</v>
       </c>
       <c r="BD35" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="BF35" t="n">
         <v>1.05</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.91</v>
+        <v>1.04</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.9</v>
+        <v>10.2</v>
       </c>
       <c r="R38" t="n">
-        <v>3.6</v>
+        <v>17.11</v>
       </c>
       <c r="S38" t="n">
-        <v>2.5</v>
+        <v>1.33</v>
       </c>
       <c r="T38" t="n">
-        <v>2.34</v>
+        <v>3.75</v>
       </c>
       <c r="U38" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="V38" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="W38" t="n">
-        <v>3.34</v>
+        <v>5</v>
       </c>
       <c r="X38" t="n">
-        <v>2.24</v>
+        <v>1.77</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.57</v>
+        <v>1.99</v>
       </c>
       <c r="Z38" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AZ38" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC38" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK38" t="n">
+      <c r="BA38" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC38" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BD38" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="Q39" t="n">
-        <v>10.2</v>
+        <v>3.9</v>
       </c>
       <c r="R39" t="n">
-        <v>17.11</v>
+        <v>3.6</v>
       </c>
       <c r="S39" t="n">
-        <v>1.33</v>
+        <v>2.5</v>
       </c>
       <c r="T39" t="n">
-        <v>3.75</v>
+        <v>2.34</v>
       </c>
       <c r="U39" t="n">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="V39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W39" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC39" t="n">
         <v>1.15</v>
       </c>
-      <c r="W39" t="n">
-        <v>5</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA39" t="n">
+      <c r="AD39" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY39" t="n">
         <v>1.3</v>
       </c>
-      <c r="AB39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AZ39" t="n">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="BA39" t="n">
-        <v>14</v>
+        <v>3.1</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="BD39" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -9281,7 +9281,7 @@
         <v>6.76</v>
       </c>
       <c r="S45" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="T45" t="n">
         <v>2.38</v>
@@ -9335,10 +9335,10 @@
         <v>1.12</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AM45" t="n">
         <v>1.13</v>
@@ -9487,16 +9487,16 @@
         <v>1.89</v>
       </c>
       <c r="V46" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="W46" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="X46" t="n">
         <v>2.67</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z46" t="n">
         <v>6.4</v>
@@ -9872,70 +9872,70 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9977,19 +9977,19 @@
         <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -1413,10 +1413,10 @@
         <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="X5" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="Y5" t="n">
         <v>1.44</v>
@@ -1428,7 +1428,7 @@
         <v>1.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC5" t="n">
         <v>1.2</v>
@@ -1437,16 +1437,16 @@
         <v>3.72</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AG5" t="n">
         <v>2.83</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AI5" t="n">
         <v>5.45</v>
@@ -1631,19 +1631,19 @@
         <v>1.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.28</v>
+        <v>3.52</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG6" t="n">
         <v>3.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AI6" t="n">
         <v>5.99</v>
@@ -1652,16 +1652,16 @@
         <v>1.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL6" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AM6" t="n">
         <v>1.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2189,7 +2189,7 @@
         <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="T9" t="n">
         <v>2.5</v>
@@ -2210,7 +2210,7 @@
         <v>1.57</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AA9" t="n">
         <v>1.12</v>
@@ -2219,7 +2219,7 @@
         <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AD9" t="n">
         <v>4.65</v>
@@ -2228,7 +2228,7 @@
         <v>1.48</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="AG9" t="n">
         <v>2.35</v>
@@ -2237,7 +2237,7 @@
         <v>1.61</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AJ9" t="n">
         <v>1.19</v>
@@ -2246,7 +2246,7 @@
         <v>1.69</v>
       </c>
       <c r="AL9" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AM9" t="n">
         <v>1.16</v>
@@ -2297,7 +2297,7 @@
         <v>1.12</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BD9" t="n">
         <v>4.75</v>
@@ -2971,10 +2971,10 @@
         <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="R13" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
         <v>2.77</v>
@@ -2986,13 +2986,13 @@
         <v>5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W13" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
       <c r="X13" t="n">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="Y13" t="n">
         <v>1.23</v>
@@ -3001,28 +3001,28 @@
         <v>10</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AE13" t="n">
         <v>2.87</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG13" t="n">
-        <v>5.1</v>
+        <v>5.65</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AI13" t="n">
         <v>11.5</v>
@@ -3031,16 +3031,16 @@
         <v>1.01</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AL13" t="n">
         <v>1.53</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3088,7 +3088,7 @@
         <v>2.82</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="BE13" t="n">
         <v>1.35</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q28" t="n">
         <v>3.7</v>
       </c>
       <c r="R28" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="S28" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="T28" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U28" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="V28" t="n">
         <v>1.26</v>
       </c>
       <c r="W28" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="X28" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Y28" t="n">
         <v>1.48</v>
@@ -5956,46 +5956,46 @@
         <v>6</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.12</v>
+        <v>4.1</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AG28" t="n">
         <v>2.7</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AI28" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6040,13 +6040,13 @@
         <v>1.14</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="BF28" t="n">
         <v>1.18</v>
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" t="n">
         <v>3.5</v>
@@ -6138,22 +6138,22 @@
         <v>3.04</v>
       </c>
       <c r="V29" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W29" t="n">
         <v>3.25</v>
       </c>
       <c r="X29" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AB29" t="n">
         <v>1.03</v>
@@ -6162,25 +6162,25 @@
         <v>1.18</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.71</v>
+        <v>1.49</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.33</v>
+        <v>2.09</v>
       </c>
       <c r="AG29" t="n">
         <v>2.23</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AI29" t="n">
         <v>4.95</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK29" t="n">
         <v>1.57</v>
@@ -6243,7 +6243,7 @@
         <v>4.25</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="BF29" t="n">
         <v>1.19</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY32" t="n">
         <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -7302,28 +7302,28 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="R35" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="U35" t="n">
         <v>4.77</v>
       </c>
       <c r="V35" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="W35" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="X35" t="n">
         <v>3.6</v>
@@ -7338,25 +7338,25 @@
         <v>1.01</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="AE35" t="n">
         <v>2.91</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AG35" t="n">
         <v>5.75</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AI35" t="n">
         <v>13</v>
@@ -7365,7 +7365,7 @@
         <v>1.03</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AL35" t="n">
         <v>1.57</v>
@@ -7422,7 +7422,7 @@
         <v>2.78</v>
       </c>
       <c r="BD35" t="n">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="BE35" t="n">
         <v>1.36</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,143 +7495,143 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>6.75</v>
+        <v>3.59</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.6</v>
+        <v>2.93</v>
       </c>
       <c r="R36" t="n">
-        <v>1.49</v>
+        <v>2.22</v>
       </c>
       <c r="S36" t="n">
-        <v>6.9</v>
+        <v>4.6</v>
       </c>
       <c r="T36" t="n">
-        <v>2.07</v>
+        <v>1.71</v>
       </c>
       <c r="U36" t="n">
-        <v>2.06</v>
+        <v>3.1</v>
       </c>
       <c r="V36" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="W36" t="n">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="X36" t="n">
-        <v>3.18</v>
+        <v>4.15</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>7.9</v>
+        <v>15</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.39</v>
+        <v>1.7</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.59</v>
+        <v>2.08</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.27</v>
+        <v>2.97</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG36" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AI36" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK36" t="n">
         <v>2.4</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AM36" t="n">
-        <v>2.16</v>
+        <v>1.4</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="AO36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AR36" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ36" t="n">
         <v>2.28</v>
       </c>
-      <c r="AS36" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BA36" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="BB36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE36" t="n">
         <v>1.3</v>
       </c>
-      <c r="BC36" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>1.46</v>
-      </c>
       <c r="BF36" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,71 +7692,71 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.59</v>
+        <v>6.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.93</v>
+        <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>2.22</v>
+        <v>1.49</v>
       </c>
       <c r="S37" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="T37" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="U37" t="n">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="V37" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="W37" t="n">
-        <v>2.15</v>
+        <v>2.43</v>
       </c>
       <c r="X37" t="n">
-        <v>4.15</v>
+        <v>3.18</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z37" t="n">
-        <v>15</v>
+        <v>7.9</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.08</v>
+        <v>2.59</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.97</v>
+        <v>2.5</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AI37" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK37" t="n">
         <v>2.4</v>
@@ -7765,70 +7765,70 @@
         <v>1.5</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.44</v>
+        <v>1.19</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AT37" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="BC37" t="n">
-        <v>3.2</v>
+        <v>2.44</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46141.60416666666</v>
@@ -8090,40 +8090,40 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q39" t="n">
         <v>3.9</v>
       </c>
       <c r="R39" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="S39" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="T39" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="U39" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="V39" t="n">
         <v>1.25</v>
       </c>
       <c r="W39" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="X39" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Z39" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AB39" t="n">
         <v>1.03</v>
@@ -8132,10 +8132,10 @@
         <v>1.15</v>
       </c>
       <c r="AD39" t="n">
-        <v>4.45</v>
+        <v>4.84</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AF39" t="n">
         <v>2.3</v>
@@ -8144,25 +8144,25 @@
         <v>2.16</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AI39" t="n">
-        <v>3.95</v>
+        <v>3.72</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL39" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AM39" t="n">
         <v>1.25</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8174,10 +8174,10 @@
         <v>1.52</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="AT39" t="n">
         <v>3.05</v>
@@ -8189,7 +8189,7 @@
         <v>2.28</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AX39" t="n">
         <v>1.49</v>
@@ -8198,13 +8198,13 @@
         <v>1.3</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BA39" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BC39" t="n">
         <v>1.75</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD45" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9666,7 +9666,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q47" t="n">
         <v>3.4</v>
@@ -9678,10 +9678,10 @@
         <v>2.62</v>
       </c>
       <c r="T47" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="U47" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="V47" t="n">
         <v>1.33</v>
@@ -9690,10 +9690,10 @@
         <v>3.18</v>
       </c>
       <c r="X47" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z47" t="n">
         <v>6.05</v>
@@ -9708,25 +9708,25 @@
         <v>1.21</v>
       </c>
       <c r="AD47" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG47" t="n">
         <v>2.94</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AI47" t="n">
         <v>5.39</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AK47" t="n">
         <v>1.61</v>
@@ -9783,7 +9783,7 @@
         <v>1.17</v>
       </c>
       <c r="BC47" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="BD47" t="n">
         <v>3.96</v>
@@ -9872,70 +9872,70 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9977,19 +9977,19 @@
         <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="BD48" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI48"/>
+  <dimension ref="A1:BI47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="R2" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="S2" t="n">
         <v>3.96</v>
@@ -855,10 +855,10 @@
         <v>2.35</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.16</v>
@@ -921,7 +921,7 @@
         <v>1.77</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="BE2" t="n">
         <v>1.92</v>
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="R3" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -1013,7 +1013,7 @@
         <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="V3" t="n">
         <v>1.38</v>
@@ -1043,10 +1043,10 @@
         <v>3.14</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG3" t="n">
         <v>2.88</v>
@@ -1055,7 +1055,7 @@
         <v>1.26</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.25</v>
+        <v>6.45</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.06</v>
@@ -1067,7 +1067,7 @@
         <v>1.96</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AN3" t="n">
         <v>1.47</v>
@@ -1115,13 +1115,13 @@
         <v>1.21</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="BD3" t="n">
         <v>3.58</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="BF3" t="n">
         <v>1.13</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.95</v>
+        <v>4.75</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="T7" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>5.39</v>
+        <v>1.81</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W7" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="X7" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="Z7" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AA7" t="n">
         <v>1.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.23</v>
+        <v>2.47</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.47</v>
+        <v>2.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AJ7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM7" t="n">
         <v>1.16</v>
       </c>
-      <c r="AK7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AN7" t="n">
-        <v>2.3</v>
+        <v>1.09</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>6.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="U9" t="n">
-        <v>1.81</v>
+        <v>5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="X9" t="n">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AF9" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="AG9" t="n">
         <v>2.35</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AJ9" t="n">
         <v>1.19</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.09</v>
+        <v>2.15</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="R23" t="n">
-        <v>1.96</v>
+        <v>1.41</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>6</v>
+        <v>3.55</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.96</v>
       </c>
       <c r="S26" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R32" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG32" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="X32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>6.1</v>
-      </c>
       <c r="AH32" t="n">
-        <v>1.05</v>
+        <v>1.37</v>
       </c>
       <c r="AI32" t="n">
-        <v>16.5</v>
+        <v>5</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.45</v>
+        <v>1.62</v>
       </c>
       <c r="AL32" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
         <v>1.44</v>
       </c>
-      <c r="AM32" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AR32" t="n">
-        <v>2.23</v>
+        <v>1.71</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>3.2</v>
+        <v>1.94</v>
       </c>
       <c r="BD32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,22 +6908,22 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -6932,10 +6932,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -6947,40 +6947,40 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -6989,49 +6989,49 @@
         <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
         <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
         <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="Q38" t="n">
-        <v>10.2</v>
+        <v>3.9</v>
       </c>
       <c r="R38" t="n">
-        <v>17.11</v>
+        <v>3.7</v>
       </c>
       <c r="S38" t="n">
-        <v>1.33</v>
+        <v>2.43</v>
       </c>
       <c r="T38" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="U38" t="n">
-        <v>12.5</v>
+        <v>3.91</v>
       </c>
       <c r="V38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC38" t="n">
         <v>1.15</v>
       </c>
-      <c r="W38" t="n">
-        <v>5</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA38" t="n">
+      <c r="AD38" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY38" t="n">
         <v>1.3</v>
       </c>
-      <c r="AB38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AL38" t="n">
+      <c r="AZ38" t="n">
         <v>1.44</v>
       </c>
-      <c r="AM38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BA38" t="n">
-        <v>14</v>
+        <v>3.2</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="BD38" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.85</v>
+        <v>1.05</v>
       </c>
       <c r="Q39" t="n">
+        <v>12</v>
+      </c>
+      <c r="R39" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T39" t="n">
         <v>3.9</v>
       </c>
-      <c r="R39" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.38</v>
-      </c>
       <c r="U39" t="n">
-        <v>3.91</v>
+        <v>12.5</v>
       </c>
       <c r="V39" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="W39" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="X39" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AL39" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z39" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB39" t="n">
+      <c r="AM39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AZ39" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC39" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BA39" t="n">
-        <v>3.2</v>
+        <v>14</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8628,12 +8628,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,79 +8681,79 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.82</v>
+        <v>1.18</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.1</v>
+        <v>8</v>
       </c>
       <c r="R42" t="n">
-        <v>2.4</v>
+        <v>13.5</v>
       </c>
       <c r="S42" t="n">
-        <v>3.4</v>
+        <v>1.53</v>
       </c>
       <c r="T42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U42" t="n">
-        <v>3.2</v>
+        <v>10.25</v>
       </c>
       <c r="V42" t="n">
-        <v>1.47</v>
+        <v>1.15</v>
       </c>
       <c r="W42" t="n">
-        <v>2.67</v>
+        <v>4.5</v>
       </c>
       <c r="X42" t="n">
-        <v>3.2</v>
+        <v>1.96</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.3</v>
+        <v>1.79</v>
       </c>
       <c r="Z42" t="n">
-        <v>8.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.03</v>
+        <v>1.18</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.84</v>
+        <v>6.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.23</v>
+        <v>1.36</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.65</v>
+        <v>2.99</v>
       </c>
       <c r="AG42" t="n">
-        <v>4.05</v>
+        <v>1.9</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AI42" t="n">
-        <v>8.300000000000001</v>
+        <v>2.89</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.95</v>
+        <v>1.56</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.33</v>
+        <v>1.07</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.42</v>
+        <v>6.35</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8762,52 +8762,52 @@
         <v>1.22</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="AU42" t="n">
         <v>3.5</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.58</v>
+        <v>2.3</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
-        <v>46141.66666666666</v>
+        <v>46141.67708333334</v>
       </c>
     </row>
     <row r="43">
@@ -8825,27 +8825,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,112 +8878,112 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.06</v>
+        <v>1.39</v>
       </c>
       <c r="Q43" t="n">
-        <v>12</v>
+        <v>4.5</v>
       </c>
       <c r="R43" t="n">
-        <v>76</v>
+        <v>6.76</v>
       </c>
       <c r="S43" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="T43" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="U43" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="V43" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="W43" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="X43" t="n">
-        <v>2.16</v>
+        <v>2.39</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="Z43" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD43" t="n">
         <v>4</v>
       </c>
-      <c r="AA43" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AE43" t="n">
-        <v>1.45</v>
+        <v>1.65</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.54</v>
+        <v>2.08</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="AI43" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AK43" t="n">
-        <v>2.38</v>
+        <v>1.84</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AN43" t="n">
-        <v>6.1</v>
+        <v>2.66</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ43" t="n">
         <v>0</v>
@@ -8992,19 +8992,19 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="BD43" t="n">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="BE43" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9013,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="BI43" s="3" t="n">
-        <v>46141.67708333334</v>
+        <v>46141.83333333334</v>
       </c>
     </row>
     <row r="44">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>6.98</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46141.83333333334</v>
+        <v>46141.875</v>
       </c>
     </row>
     <row r="46">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>6.98</v>
+        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="R46" t="n">
-        <v>1.41</v>
+        <v>3</v>
       </c>
       <c r="S46" t="n">
-        <v>7.19</v>
+        <v>2.62</v>
       </c>
       <c r="T46" t="n">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="U46" t="n">
-        <v>1.89</v>
+        <v>3.66</v>
       </c>
       <c r="V46" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W46" t="n">
-        <v>2.92</v>
+        <v>3.18</v>
       </c>
       <c r="X46" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="Z46" t="n">
-        <v>6.4</v>
+        <v>6.05</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AB46" t="n">
         <v>1</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AD46" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG46" t="n">
-        <v>3.08</v>
+        <v>2.94</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AI46" t="n">
-        <v>5.9</v>
+        <v>5.39</v>
       </c>
       <c r="AJ46" t="n">
         <v>1.09</v>
       </c>
       <c r="AK46" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.03</v>
+        <v>1.67</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9583,19 +9583,19 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="BC46" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="BD46" t="n">
-        <v>3.9</v>
+        <v>3.96</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9604,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="BI46" s="3" t="n">
-        <v>46141.875</v>
+        <v>46141.91666666666</v>
       </c>
     </row>
     <row r="47">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,79 +9666,79 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9780,19 +9780,19 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9801,203 +9801,6 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46141.91666666666</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>46141</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Portland Thorns</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI48" s="3" t="n">
         <v>46141.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -804,13 +804,13 @@
         <v>3.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="R2" t="n">
         <v>1.85</v>
       </c>
       <c r="S2" t="n">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="T2" t="n">
         <v>2.18</v>
@@ -873,7 +873,7 @@
         <v>1.16</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -1013,7 +1013,7 @@
         <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="V3" t="n">
         <v>1.38</v>
@@ -1040,34 +1040,34 @@
         <v>1.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.14</v>
+        <v>3.36</v>
       </c>
       <c r="AE3" t="n">
         <v>1.99</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AG3" t="n">
         <v>2.88</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AI3" t="n">
         <v>6.45</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AL3" t="n">
         <v>1.96</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AN3" t="n">
         <v>1.47</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="Q9" t="n">
         <v>4.2</v>
@@ -2195,19 +2195,19 @@
         <v>2.35</v>
       </c>
       <c r="U9" t="n">
-        <v>5</v>
+        <v>5.64</v>
       </c>
       <c r="V9" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
         <v>3.2</v>
       </c>
       <c r="X9" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
         <v>5.05</v>
@@ -2240,7 +2240,7 @@
         <v>4.1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK9" t="n">
         <v>1.67</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>6</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.41</v>
+        <v>3.35</v>
       </c>
       <c r="S23" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q24" t="n">
         <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>2.37</v>
+        <v>1.96</v>
       </c>
       <c r="S24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>6</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="R25" t="n">
-        <v>3.35</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="R31" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AG31" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R31" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="X31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>6.1</v>
-      </c>
       <c r="AH31" t="n">
-        <v>1.05</v>
+        <v>1.37</v>
       </c>
       <c r="AI31" t="n">
-        <v>16.5</v>
+        <v>5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.45</v>
+        <v>1.62</v>
       </c>
       <c r="AL31" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
         <v>1.44</v>
       </c>
-      <c r="AM31" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AR31" t="n">
-        <v>2.23</v>
+        <v>1.71</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>3.2</v>
+        <v>1.94</v>
       </c>
       <c r="BD31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,22 +6711,22 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6735,10 +6735,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -6750,40 +6750,40 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6792,49 +6792,49 @@
         <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
         <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
         <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="R34" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC34" t="n">
         <v>1.8</v>
       </c>
-      <c r="U34" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="W34" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AD34" t="n">
-        <v>2.33</v>
+        <v>2.06</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AG34" t="n">
-        <v>5.75</v>
+        <v>6.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AI34" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AL34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AW34" t="n">
         <v>1.57</v>
       </c>
-      <c r="AM34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AX34" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,71 +7495,71 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.59</v>
+        <v>6.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.93</v>
+        <v>3.6</v>
       </c>
       <c r="R36" t="n">
-        <v>2.22</v>
+        <v>1.49</v>
       </c>
       <c r="S36" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="T36" t="n">
-        <v>1.71</v>
+        <v>2.08</v>
       </c>
       <c r="U36" t="n">
-        <v>3.1</v>
+        <v>2.07</v>
       </c>
       <c r="V36" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="W36" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="X36" t="n">
-        <v>4.15</v>
+        <v>3.18</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="Z36" t="n">
-        <v>15</v>
+        <v>7.9</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.08</v>
+        <v>2.59</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.97</v>
+        <v>2.5</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AI36" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK36" t="n">
         <v>2.4</v>
@@ -7568,70 +7568,70 @@
         <v>1.5</v>
       </c>
       <c r="AM36" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BH36" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH36" t="n">
-        <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,71 +7692,71 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>6.75</v>
+        <v>3.59</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>2.93</v>
       </c>
       <c r="R37" t="n">
-        <v>1.49</v>
+        <v>2.22</v>
       </c>
       <c r="S37" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="T37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2</v>
+      </c>
+      <c r="X37" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD37" t="n">
         <v>2.08</v>
       </c>
-      <c r="U37" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="X37" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>2.59</v>
-      </c>
       <c r="AE37" t="n">
-        <v>2.5</v>
+        <v>2.97</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG37" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AI37" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK37" t="n">
         <v>2.4</v>
@@ -7765,70 +7765,70 @@
         <v>1.5</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="AO37" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AR37" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ37" t="n">
         <v>2.28</v>
       </c>
-      <c r="AS37" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BA37" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="BB37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE37" t="n">
         <v>1.3</v>
       </c>
-      <c r="BC37" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.46</v>
-      </c>
       <c r="BF37" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.85</v>
+        <v>1.04</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.9</v>
+        <v>12</v>
       </c>
       <c r="R38" t="n">
-        <v>3.7</v>
+        <v>23.19</v>
       </c>
       <c r="S38" t="n">
-        <v>2.43</v>
+        <v>1.33</v>
       </c>
       <c r="T38" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="U38" t="n">
-        <v>3.91</v>
+        <v>12.2</v>
       </c>
       <c r="V38" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="W38" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="X38" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AZ38" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC38" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BA38" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.91</v>
+        <v>2.65</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.05</v>
+        <v>1.85</v>
       </c>
       <c r="Q39" t="n">
-        <v>12</v>
+        <v>3.9</v>
       </c>
       <c r="R39" t="n">
-        <v>23.19</v>
+        <v>3.7</v>
       </c>
       <c r="S39" t="n">
-        <v>1.33</v>
+        <v>2.43</v>
       </c>
       <c r="T39" t="n">
-        <v>3.9</v>
+        <v>2.38</v>
       </c>
       <c r="U39" t="n">
-        <v>12.5</v>
+        <v>3.91</v>
       </c>
       <c r="V39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X39" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB39" t="n">
         <v>1.12</v>
       </c>
-      <c r="W39" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>1.05</v>
-      </c>
       <c r="BC39" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="BD39" t="n">
-        <v>7.8</v>
+        <v>4.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.55</v>
+        <v>1.91</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Q42" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="R42" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="S42" t="n">
         <v>1.53</v>
@@ -8711,7 +8711,7 @@
         <v>1.79</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA42" t="n">
         <v>1.18</v>
@@ -8723,10 +8723,10 @@
         <v>1.1</v>
       </c>
       <c r="AD42" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AF42" t="n">
         <v>2.99</v>
@@ -8735,13 +8735,13 @@
         <v>1.9</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AI42" t="n">
         <v>2.89</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AK42" t="n">
         <v>2.38</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -804,13 +804,13 @@
         <v>3.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
       <c r="R2" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="S2" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="T2" t="n">
         <v>2.18</v>
@@ -819,7 +819,7 @@
         <v>2.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
         <v>3.14</v>
@@ -855,7 +855,7 @@
         <v>2.35</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AI2" t="n">
         <v>3.95</v>
@@ -870,10 +870,10 @@
         <v>2.4</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -1013,7 +1013,7 @@
         <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="V3" t="n">
         <v>1.38</v>
@@ -1043,16 +1043,16 @@
         <v>3.36</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
         <v>2.88</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AI3" t="n">
         <v>6.45</v>
@@ -1067,7 +1067,7 @@
         <v>1.96</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AN3" t="n">
         <v>1.47</v>
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q5" t="n">
         <v>3.4</v>
@@ -1419,7 +1419,7 @@
         <v>2.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Z5" t="n">
         <v>6.5</v>
@@ -1434,7 +1434,7 @@
         <v>1.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.72</v>
+        <v>3.83</v>
       </c>
       <c r="AE5" t="n">
         <v>1.78</v>
@@ -1446,7 +1446,7 @@
         <v>2.83</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AI5" t="n">
         <v>5.45</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="R9" t="n">
-        <v>5</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>5.65</v>
       </c>
       <c r="T9" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>5.64</v>
+        <v>1.85</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="W9" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="X9" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.05</v>
+        <v>4.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AB9" t="n">
         <v>1.02</v>
       </c>
       <c r="AC9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.16</v>
       </c>
       <c r="AK9" t="n">
         <v>1.67</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.15</v>
+        <v>1.11</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>3.55</v>
       </c>
       <c r="Q23" t="n">
         <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>3.35</v>
+        <v>1.96</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.96</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>6</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.41</v>
+        <v>3.35</v>
       </c>
       <c r="S25" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.64</v>
+        <v>2.6</v>
       </c>
       <c r="R31" t="n">
-        <v>3.44</v>
+        <v>3.05</v>
       </c>
       <c r="S31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
         <v>2.5</v>
       </c>
-      <c r="T31" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U31" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
       <c r="AV31" t="n">
-        <v>2.55</v>
+        <v>1.92</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.63</v>
+        <v>1.34</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.94</v>
+        <v>3.2</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="X35" t="n">
         <v>2.65</v>
       </c>
-      <c r="R35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U35" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="V35" t="n">
+      <c r="Y35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK35" t="n">
         <v>1.62</v>
       </c>
-      <c r="W35" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y35" t="n">
+      <c r="AL35" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BB35" t="n">
         <v>1.19</v>
       </c>
-      <c r="Z35" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR35" t="n">
+      <c r="BC35" t="n">
         <v>2.02</v>
       </c>
-      <c r="AS35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>2.78</v>
-      </c>
       <c r="BD35" t="n">
-        <v>2.85</v>
+        <v>3.92</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,143 +7495,143 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>6.75</v>
+        <v>3.59</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.6</v>
+        <v>2.93</v>
       </c>
       <c r="R36" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AL36" t="n">
         <v>1.49</v>
       </c>
-      <c r="S36" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AA36" t="n">
+      <c r="AM36" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BF36" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB36" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>1.08</v>
-      </c>
       <c r="BG36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH36" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,71 +7692,71 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.59</v>
+        <v>6.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.93</v>
+        <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>2.22</v>
+        <v>1.49</v>
       </c>
       <c r="S37" t="n">
-        <v>4.6</v>
+        <v>7.71</v>
       </c>
       <c r="T37" t="n">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="U37" t="n">
-        <v>3.1</v>
+        <v>2.07</v>
       </c>
       <c r="V37" t="n">
-        <v>1.65</v>
+        <v>1.46</v>
       </c>
       <c r="W37" t="n">
-        <v>2</v>
+        <v>2.59</v>
       </c>
       <c r="X37" t="n">
-        <v>4.15</v>
+        <v>3.18</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="Z37" t="n">
-        <v>15</v>
+        <v>7.9</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.08</v>
+        <v>2.59</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.97</v>
+        <v>2.25</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AG37" t="n">
-        <v>6.5</v>
+        <v>4.29</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AI37" t="n">
-        <v>11</v>
+        <v>7.9</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK37" t="n">
         <v>2.4</v>
@@ -7765,13 +7765,13 @@
         <v>1.5</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP37" t="n">
         <v>1.45</v>
@@ -7780,55 +7780,55 @@
         <v>1.75</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AT37" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AW37" t="n">
         <v>1.58</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2.28</v>
+        <v>3.55</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="BC37" t="n">
-        <v>3.08</v>
+        <v>2.44</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="Q38" t="n">
-        <v>12</v>
+        <v>3.9</v>
       </c>
       <c r="R38" t="n">
-        <v>23.19</v>
+        <v>3.7</v>
       </c>
       <c r="S38" t="n">
-        <v>1.33</v>
+        <v>2.43</v>
       </c>
       <c r="T38" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="U38" t="n">
-        <v>12.2</v>
+        <v>3.91</v>
       </c>
       <c r="V38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BB38" t="n">
         <v>1.12</v>
       </c>
-      <c r="W38" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BC38" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="BD38" t="n">
-        <v>7.8</v>
+        <v>4.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.65</v>
+        <v>1.91</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.85</v>
+        <v>1.04</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.9</v>
+        <v>12</v>
       </c>
       <c r="R39" t="n">
-        <v>3.7</v>
+        <v>23.19</v>
       </c>
       <c r="S39" t="n">
-        <v>2.43</v>
+        <v>1.33</v>
       </c>
       <c r="T39" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="U39" t="n">
-        <v>3.91</v>
+        <v>12.2</v>
       </c>
       <c r="V39" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="W39" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="X39" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AZ39" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC39" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BA39" t="n">
-        <v>3.2</v>
+        <v>15</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.91</v>
+        <v>2.65</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,79 +8878,79 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>6.76</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8992,19 +8992,19 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.63</v>
+        <v>6.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.83</v>
+        <v>4.6</v>
       </c>
       <c r="R7" t="n">
-        <v>4.6</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.16</v>
+        <v>5.65</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z7" t="n">
         <v>4.8</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W7" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AA7" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AB7" t="n">
         <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.1</v>
+        <v>4.55</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AI7" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.01</v>
+        <v>1.11</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2574,16 +2574,16 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q11" t="n">
         <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="S11" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="T11" t="n">
         <v>1.97</v>
@@ -2592,22 +2592,22 @@
         <v>5</v>
       </c>
       <c r="V11" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="W11" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="X11" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
         <v>10</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB11" t="n">
         <v>1.08</v>
@@ -2622,10 +2622,10 @@
         <v>2.87</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AG11" t="n">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="AH11" t="n">
         <v>1.08</v>
@@ -2640,13 +2640,13 @@
         <v>2.25</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2694,7 +2694,7 @@
         <v>2.82</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="BE11" t="n">
         <v>1.35</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="Q23" t="n">
         <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>3.17</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="R25" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -6120,28 +6120,28 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="R29" t="n">
         <v>2.37</v>
       </c>
       <c r="S29" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="T29" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="U29" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="V29" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W29" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="X29" t="n">
         <v>2.5</v>
@@ -6156,10 +6156,10 @@
         <v>1.07</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AD29" t="n">
         <v>3.9</v>
@@ -6168,19 +6168,19 @@
         <v>1.49</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.23</v>
+        <v>2.69</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AI29" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK29" t="n">
         <v>1.57</v>
@@ -6189,10 +6189,10 @@
         <v>2.25</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6237,13 +6237,13 @@
         <v>1.16</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="BD29" t="n">
         <v>4.25</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="BF29" t="n">
         <v>1.19</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W32" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="X32" t="n">
         <v>2.65</v>
       </c>
-      <c r="R32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U32" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="V32" t="n">
+      <c r="Y32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK32" t="n">
         <v>1.62</v>
       </c>
-      <c r="W32" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AL32" t="n">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.51</v>
+        <v>1.87</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AR32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC32" t="n">
         <v>2.02</v>
       </c>
-      <c r="AS32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.78</v>
-      </c>
       <c r="BD32" t="n">
-        <v>2.85</v>
+        <v>3.92</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7383,52 +7383,52 @@
         <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
         <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7499,34 +7499,34 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.59</v>
+        <v>3.8</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="R36" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="S36" t="n">
         <v>4.6</v>
       </c>
       <c r="T36" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="U36" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="V36" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W36" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="X36" t="n">
-        <v>4.15</v>
+        <v>3.98</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z36" t="n">
         <v>9.5</v>
@@ -7535,25 +7535,25 @@
         <v>1.01</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AG36" t="n">
         <v>6.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AI36" t="n">
         <v>11</v>
@@ -7562,16 +7562,16 @@
         <v>1.03</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AM36" t="n">
         <v>1.34</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7586,22 +7586,22 @@
         <v>2.24</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AT36" t="n">
         <v>4.28</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AY36" t="n">
         <v>1.23</v>
@@ -7613,19 +7613,19 @@
         <v>1.55</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BC36" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7714,16 +7714,16 @@
         <v>2.07</v>
       </c>
       <c r="V37" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W37" t="n">
         <v>2.59</v>
       </c>
       <c r="X37" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z37" t="n">
         <v>7.9</v>
@@ -7732,22 +7732,22 @@
         <v>1.02</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AC37" t="n">
         <v>1.39</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AE37" t="n">
         <v>2.25</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG37" t="n">
-        <v>4.29</v>
+        <v>4.1</v>
       </c>
       <c r="AH37" t="n">
         <v>1.16</v>
@@ -7813,13 +7813,13 @@
         <v>1.3</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="BF37" t="n">
         <v>1.08</v>
@@ -8090,7 +8090,7 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Q39" t="n">
         <v>12</v>
@@ -8099,7 +8099,7 @@
         <v>23.19</v>
       </c>
       <c r="S39" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T39" t="n">
         <v>3.75</v>
@@ -8135,34 +8135,34 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AF39" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="AG39" t="n">
         <v>1.65</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AI39" t="n">
         <v>2.24</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AM39" t="n">
         <v>1.04</v>
       </c>
       <c r="AN39" t="n">
-        <v>6.55</v>
+        <v>8.5</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8213,7 +8213,7 @@
         <v>7.8</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="BF39" t="n">
         <v>1.58</v>
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="R40" t="n">
         <v>2.62</v>
       </c>
       <c r="S40" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T40" t="n">
         <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V40" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W40" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="X40" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA40" t="n">
         <v>1.03</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AE40" t="n">
         <v>2.23</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AG40" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AH40" t="n">
         <v>1.18</v>
       </c>
       <c r="AI40" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AJ40" t="n">
         <v>1.06</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="AV40" t="n">
         <v>2.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Q42" t="n">
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
       <c r="R42" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="S42" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="T42" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="U42" t="n">
-        <v>10.25</v>
+        <v>11.5</v>
       </c>
       <c r="V42" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W42" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="X42" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AB42" t="n">
         <v>1.02</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AD42" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AI42" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AK42" t="n">
         <v>2.38</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AN42" t="n">
-        <v>6.35</v>
+        <v>7.4</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.92</v>
+        <v>2.55</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BB42" t="n">
         <v>1.15</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BD42" t="n">
         <v>4.8</v>
       </c>
       <c r="BE42" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9075,16 +9075,16 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="R44" t="n">
-        <v>6.76</v>
+        <v>6</v>
       </c>
       <c r="S44" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="T44" t="n">
         <v>2.38</v>
@@ -9093,10 +9093,10 @@
         <v>6.5</v>
       </c>
       <c r="V44" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W44" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="X44" t="n">
         <v>2.39</v>
@@ -9117,37 +9117,37 @@
         <v>1.17</v>
       </c>
       <c r="AD44" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AI44" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AJ44" t="n">
         <v>1.12</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AM44" t="n">
         <v>1.13</v>
       </c>
       <c r="AN44" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9281,19 +9281,19 @@
         <v>1.41</v>
       </c>
       <c r="S45" t="n">
-        <v>7.19</v>
+        <v>6.81</v>
       </c>
       <c r="T45" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="U45" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="V45" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W45" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="X45" t="n">
         <v>2.67</v>
@@ -9317,16 +9317,16 @@
         <v>3.42</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AG45" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AI45" t="n">
         <v>5.9</v>
@@ -9341,10 +9341,10 @@
         <v>1.7</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AN45" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9389,13 +9389,13 @@
         <v>1.21</v>
       </c>
       <c r="BC45" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BD45" t="n">
         <v>3.9</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="BF45" t="n">
         <v>1.17</v>
@@ -9469,7 +9469,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q46" t="n">
         <v>3.4</v>
@@ -9484,7 +9484,7 @@
         <v>2.17</v>
       </c>
       <c r="U46" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="V46" t="n">
         <v>1.33</v>
@@ -9493,10 +9493,10 @@
         <v>3.18</v>
       </c>
       <c r="X46" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Z46" t="n">
         <v>6.05</v>
@@ -9508,10 +9508,10 @@
         <v>1</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AD46" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AE46" t="n">
         <v>1.76</v>
@@ -9532,16 +9532,16 @@
         <v>1.09</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AL46" t="n">
         <v>2.15</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9675,70 +9675,70 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9780,19 +9780,19 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.51</v>
+        <v>3.14</v>
       </c>
       <c r="R2" t="n">
-        <v>1.97</v>
+        <v>2.84</v>
       </c>
       <c r="S2" t="n">
-        <v>3.96</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
-        <v>2.4</v>
+        <v>3.64</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="X2" t="n">
-        <v>2.38</v>
+        <v>2.79</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="Z2" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AB2" t="n">
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.23</v>
+        <v>1.81</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.95</v>
+        <v>6.45</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.4</v>
+        <v>1.99</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.65</v>
+        <v>3.58</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="R3" t="n">
-        <v>2.82</v>
+        <v>1.91</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>3.98</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>3.66</v>
+        <v>2.28</v>
       </c>
       <c r="V3" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6</v>
+        <v>3.14</v>
       </c>
       <c r="X3" t="n">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AB3" t="n">
         <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.36</v>
+        <v>4.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.28</v>
+        <v>1.51</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.45</v>
+        <v>3.95</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1395,13 +1395,13 @@
         <v>3.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S5" t="n">
-        <v>3.6</v>
+        <v>3.98</v>
       </c>
       <c r="T5" t="n">
         <v>2.25</v>
@@ -1416,7 +1416,7 @@
         <v>2.92</v>
       </c>
       <c r="X5" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="Y5" t="n">
         <v>1.41</v>
@@ -1425,7 +1425,7 @@
         <v>6.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AB5" t="n">
         <v>1.04</v>
@@ -1595,7 +1595,7 @@
         <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S6" t="n">
         <v>3.34</v>
@@ -1607,10 +1607,10 @@
         <v>2.97</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="X6" t="n">
         <v>2.82</v>
@@ -1637,7 +1637,7 @@
         <v>1.91</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AG6" t="n">
         <v>3.19</v>
@@ -1795,13 +1795,13 @@
         <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="T7" t="n">
         <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V7" t="n">
         <v>1.24</v>
@@ -1822,25 +1822,25 @@
         <v>1.12</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AD7" t="n">
         <v>4.55</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG7" t="n">
         <v>2.25</v>
       </c>
-      <c r="AG7" t="n">
-        <v>2.39</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="AI7" t="n">
         <v>3.9</v>
@@ -1912,7 +1912,7 @@
         <v>1.95</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1989,16 +1989,16 @@
         <v>3.83</v>
       </c>
       <c r="R8" t="n">
-        <v>4.6</v>
+        <v>4.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="T8" t="n">
         <v>2.28</v>
       </c>
       <c r="U8" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="V8" t="n">
         <v>1.28</v>
@@ -2007,16 +2007,16 @@
         <v>3.14</v>
       </c>
       <c r="X8" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AB8" t="n">
         <v>1.02</v>
@@ -2031,10 +2031,10 @@
         <v>1.61</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="AH8" t="n">
         <v>1.47</v>
@@ -2043,19 +2043,19 @@
         <v>4.3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
         <v>1.62</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2100,13 +2100,13 @@
         <v>1.14</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="BF8" t="n">
         <v>1.23</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.6</v>
+        <v>5.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="R23" t="n">
-        <v>2.38</v>
+        <v>1.48</v>
       </c>
       <c r="S23" t="n">
-        <v>3.35</v>
+        <v>5.35</v>
       </c>
       <c r="T23" t="n">
-        <v>2.08</v>
+        <v>2.64</v>
       </c>
       <c r="U23" t="n">
-        <v>3.02</v>
+        <v>1.81</v>
       </c>
       <c r="V23" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="W23" t="n">
-        <v>2.85</v>
+        <v>4.1</v>
       </c>
       <c r="X23" t="n">
-        <v>2.62</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>6.3</v>
+        <v>4.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AB23" t="n">
         <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.5</v>
+        <v>5.52</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.96</v>
+        <v>2.1</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="AI23" t="n">
-        <v>5.37</v>
+        <v>3.7</v>
       </c>
       <c r="AJ23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AM23" t="n">
         <v>1.14</v>
       </c>
-      <c r="AK23" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AN23" t="n">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.99</v>
+        <v>1.65</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>6</v>
+        <v>3.17</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.75</v>
+        <v>2.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>2.2</v>
       </c>
       <c r="S24" t="n">
-        <v>5.5</v>
+        <v>4.08</v>
       </c>
       <c r="T24" t="n">
-        <v>2.64</v>
+        <v>1.91</v>
       </c>
       <c r="U24" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK24" t="n">
         <v>1.81</v>
       </c>
-      <c r="V24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AJ24" t="n">
+      <c r="AL24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
         <v>1.25</v>
       </c>
-      <c r="AK24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BC24" t="n">
-        <v>1.66</v>
+        <v>2.23</v>
       </c>
       <c r="BD24" t="n">
-        <v>5</v>
+        <v>3.36</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.17</v>
+        <v>2.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S25" t="n">
-        <v>4.08</v>
+        <v>3.35</v>
       </c>
       <c r="T25" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="U25" t="n">
         <v>3.02</v>
       </c>
       <c r="V25" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W25" t="n">
-        <v>2.44</v>
+        <v>2.85</v>
       </c>
       <c r="X25" t="n">
-        <v>2.99</v>
+        <v>2.62</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z25" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AI25" t="n">
-        <v>6.65</v>
+        <v>5.37</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.9</v>
+        <v>2.17</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.36</v>
+        <v>4.05</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5923,22 +5923,22 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R28" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S28" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
         <v>2.36</v>
       </c>
       <c r="U28" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="V28" t="n">
         <v>1.26</v>
@@ -5947,10 +5947,10 @@
         <v>3.32</v>
       </c>
       <c r="X28" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Z28" t="n">
         <v>6</v>
@@ -5968,88 +5968,88 @@
         <v>4.1</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG28" t="n">
         <v>2.7</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AI28" t="n">
         <v>4.9</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK28" t="n">
         <v>1.56</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AM28" t="n">
         <v>1.24</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.44</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.8</v>
+        <v>3.34</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.35</v>
+        <v>3.14</v>
       </c>
       <c r="AV28" t="n">
         <v>2.45</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="BB28" t="n">
         <v>1.14</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="BE28" t="n">
         <v>1.79</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.91</v>
+        <v>2.27</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="R32" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="S32" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="U32" t="n">
-        <v>4.33</v>
+        <v>4.77</v>
       </c>
       <c r="V32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AF32" t="n">
         <v>1.36</v>
       </c>
-      <c r="W32" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AG32" t="n">
-        <v>2.89</v>
+        <v>5.75</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="AI32" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.62</v>
+        <v>2.23</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.04</v>
+        <v>1.57</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="AS32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV32" t="n">
         <v>2.1</v>
       </c>
-      <c r="AT32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AW32" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.02</v>
+        <v>2.78</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.92</v>
+        <v>2.66</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.74</v>
+        <v>1.36</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.62</v>
+        <v>1.91</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="S34" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="T34" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="U34" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="V34" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="W34" t="n">
-        <v>1.92</v>
+        <v>3.18</v>
       </c>
       <c r="X34" t="n">
-        <v>4.4</v>
+        <v>2.65</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="Z34" t="n">
-        <v>15</v>
+        <v>6.1</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.06</v>
+        <v>3.81</v>
       </c>
       <c r="AE34" t="n">
-        <v>3.5</v>
+        <v>1.86</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.26</v>
+        <v>1.97</v>
       </c>
       <c r="AG34" t="n">
-        <v>6.1</v>
+        <v>2.89</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="AI34" t="n">
-        <v>16.5</v>
+        <v>5</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.48</v>
+        <v>1.62</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.23</v>
+        <v>1.71</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="BC34" t="n">
-        <v>3.1</v>
+        <v>2.02</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.38</v>
+        <v>3.92</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.28</v>
+        <v>1.74</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7893,34 +7893,34 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="R38" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="S38" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="T38" t="n">
         <v>2.38</v>
       </c>
       <c r="U38" t="n">
-        <v>3.91</v>
+        <v>3.4</v>
       </c>
       <c r="V38" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W38" t="n">
         <v>3.7</v>
       </c>
       <c r="X38" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Z38" t="n">
         <v>4.8</v>
@@ -7941,7 +7941,7 @@
         <v>1.48</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AG38" t="n">
         <v>2.16</v>
@@ -7959,19 +7959,19 @@
         <v>1.48</v>
       </c>
       <c r="AL38" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AM38" t="n">
         <v>1.25</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.52</v>
@@ -7980,34 +7980,34 @@
         <v>1.84</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AV38" t="n">
         <v>2.28</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="BA38" t="n">
         <v>3.2</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BC38" t="n">
         <v>1.75</v>
@@ -8287,19 +8287,19 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.19</v>
+        <v>2.96</v>
       </c>
       <c r="R40" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="S40" t="n">
         <v>3.35</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U40" t="n">
         <v>3.1</v>
@@ -8308,13 +8308,13 @@
         <v>1.46</v>
       </c>
       <c r="W40" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="X40" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z40" t="n">
         <v>7</v>
@@ -8326,16 +8326,16 @@
         <v>1.07</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="AE40" t="n">
         <v>2.23</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG40" t="n">
         <v>4.2</v>
@@ -8344,19 +8344,19 @@
         <v>1.18</v>
       </c>
       <c r="AI40" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="AJ40" t="n">
         <v>1.06</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AN40" t="n">
         <v>1.41</v>
@@ -8371,19 +8371,19 @@
         <v>1.46</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AS40" t="n">
         <v>2.19</v>
       </c>
       <c r="AT40" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AU40" t="n">
         <v>3.41</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="AW40" t="n">
         <v>1.96</v>
@@ -8392,28 +8392,28 @@
         <v>1.6</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AZ40" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BA40" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8681,22 +8681,22 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Q42" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="R42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S42" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T42" t="n">
         <v>3.04</v>
       </c>
       <c r="U42" t="n">
-        <v>11.5</v>
+        <v>11.25</v>
       </c>
       <c r="V42" t="n">
         <v>1.14</v>
@@ -8705,13 +8705,13 @@
         <v>4.65</v>
       </c>
       <c r="X42" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA42" t="n">
         <v>1.2</v>
@@ -8723,10 +8723,10 @@
         <v>1.09</v>
       </c>
       <c r="AD42" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF42" t="n">
         <v>3.12</v>
@@ -8741,7 +8741,7 @@
         <v>2.8</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AK42" t="n">
         <v>2.38</v>
@@ -8750,10 +8750,10 @@
         <v>1.7</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AN42" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8795,19 +8795,19 @@
         <v>8</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BC42" t="n">
         <v>1.52</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.8</v>
+        <v>7.3</v>
       </c>
       <c r="BE42" t="n">
         <v>2.36</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,79 +8878,79 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.84</v>
+        <v>1.36</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="R43" t="n">
-        <v>2.26</v>
+        <v>6</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8992,19 +8992,19 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.36</v>
+        <v>2.84</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="R44" t="n">
-        <v>6</v>
+        <v>2.26</v>
       </c>
       <c r="S44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.63</v>
+        <v>6.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.83</v>
+        <v>4.6</v>
       </c>
       <c r="R8" t="n">
-        <v>4.53</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>2.17</v>
+        <v>5.55</v>
       </c>
       <c r="T8" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>4.75</v>
+        <v>1.86</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="X8" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.1</v>
+        <v>4.55</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.35</v>
+        <v>4.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.17</v>
+        <v>2.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="S24" t="n">
-        <v>4.08</v>
+        <v>3.35</v>
       </c>
       <c r="T24" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="U24" t="n">
         <v>3.02</v>
       </c>
       <c r="V24" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W24" t="n">
-        <v>2.44</v>
+        <v>2.85</v>
       </c>
       <c r="X24" t="n">
-        <v>2.99</v>
+        <v>2.62</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z24" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AI24" t="n">
-        <v>6.65</v>
+        <v>5.37</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.9</v>
+        <v>2.17</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.36</v>
+        <v>4.05</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.62</v>
+        <v>1.91</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="S31" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="T31" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="U31" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="V31" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="W31" t="n">
-        <v>1.92</v>
+        <v>3.18</v>
       </c>
       <c r="X31" t="n">
-        <v>4.4</v>
+        <v>2.65</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.14</v>
+        <v>1.42</v>
       </c>
       <c r="Z31" t="n">
-        <v>15</v>
+        <v>6.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.06</v>
+        <v>3.81</v>
       </c>
       <c r="AE31" t="n">
-        <v>3.5</v>
+        <v>1.86</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.26</v>
+        <v>1.97</v>
       </c>
       <c r="AG31" t="n">
-        <v>6.1</v>
+        <v>2.89</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="AI31" t="n">
-        <v>16.5</v>
+        <v>5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.48</v>
+        <v>1.62</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.23</v>
+        <v>1.71</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.92</v>
+        <v>2.55</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.34</v>
+        <v>1.63</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="BC31" t="n">
-        <v>3.1</v>
+        <v>2.02</v>
       </c>
       <c r="BD31" t="n">
-        <v>2.38</v>
+        <v>3.92</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.28</v>
+        <v>1.74</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.27</v>
+        <v>2.62</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="R32" t="n">
-        <v>3.52</v>
+        <v>2.9</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T32" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="U32" t="n">
-        <v>4.77</v>
+        <v>4.2</v>
       </c>
       <c r="V32" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="W32" t="n">
-        <v>2.22</v>
+        <v>1.92</v>
       </c>
       <c r="X32" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="Z32" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.91</v>
+        <v>3.5</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AG32" t="n">
-        <v>5.75</v>
+        <v>6.1</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AI32" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK32" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AR32" t="n">
         <v>2.23</v>
       </c>
-      <c r="AL32" t="n">
+      <c r="AS32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AW32" t="n">
         <v>1.57</v>
       </c>
-      <c r="AM32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AX32" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="BD32" t="n">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>4.77</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7186,52 +7186,52 @@
         <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
         <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.42</v>
+        <v>3.4</v>
       </c>
       <c r="Q2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W2" t="n">
         <v>3.14</v>
       </c>
-      <c r="R2" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.6</v>
-      </c>
       <c r="X2" t="n">
-        <v>2.79</v>
+        <v>2.38</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="Z2" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AB2" t="n">
         <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.81</v>
+        <v>2.23</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.45</v>
+        <v>3.95</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.46</v>
+        <v>1.24</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.58</v>
+        <v>4.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.7</v>
+        <v>3.14</v>
       </c>
       <c r="R3" t="n">
-        <v>1.91</v>
+        <v>2.84</v>
       </c>
       <c r="S3" t="n">
-        <v>3.98</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>2.28</v>
+        <v>3.64</v>
       </c>
       <c r="V3" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="W3" t="n">
-        <v>3.14</v>
+        <v>2.6</v>
       </c>
       <c r="X3" t="n">
-        <v>2.38</v>
+        <v>2.79</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
         <v>1.01</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.23</v>
+        <v>1.81</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>3.95</v>
+        <v>6.45</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.4</v>
+        <v>1.99</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.5</v>
+        <v>3.58</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,80 +4741,80 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>3.17</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="R22" t="n">
-        <v>3.43</v>
+        <v>2.2</v>
       </c>
       <c r="S22" t="n">
-        <v>2.55</v>
+        <v>4.08</v>
       </c>
       <c r="T22" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="U22" t="n">
-        <v>4.11</v>
+        <v>3.02</v>
       </c>
       <c r="V22" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="W22" t="n">
-        <v>2.9</v>
+        <v>2.44</v>
       </c>
       <c r="X22" t="n">
-        <v>2.62</v>
+        <v>2.99</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.22</v>
       </c>
-      <c r="AD22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE22" t="n">
+      <c r="AI22" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK22" t="n">
         <v>1.81</v>
       </c>
-      <c r="AF22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AH22" t="n">
+      <c r="AL22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN22" t="n">
         <v>1.33</v>
       </c>
-      <c r="AI22" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.01</v>
+        <v>2.23</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.92</v>
+        <v>3.36</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>4.08</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5926,25 +5926,25 @@
         <v>3.13</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R28" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="S28" t="n">
         <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="U28" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="V28" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="W28" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="X28" t="n">
         <v>2.41</v>
@@ -5965,31 +5965,31 @@
         <v>1.21</v>
       </c>
       <c r="AD28" t="n">
-        <v>4.1</v>
+        <v>4.14</v>
       </c>
       <c r="AE28" t="n">
         <v>1.67</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AG28" t="n">
         <v>2.7</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AI28" t="n">
         <v>4.9</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AK28" t="n">
         <v>1.56</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AM28" t="n">
         <v>1.24</v>
@@ -6019,7 +6019,7 @@
         <v>3.14</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="AW28" t="n">
         <v>1.78</v>
@@ -6040,10 +6040,10 @@
         <v>1.14</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BE28" t="n">
         <v>1.79</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.62</v>
+        <v>2.27</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="R32" t="n">
-        <v>2.9</v>
+        <v>3.52</v>
       </c>
       <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT32" t="n">
         <v>3.4</v>
       </c>
-      <c r="T32" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="X32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AF32" t="n">
+      <c r="AU32" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY32" t="n">
         <v>1.26</v>
       </c>
-      <c r="AG32" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AH32" t="n">
+      <c r="AZ32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BF32" t="n">
         <v>1.05</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.02</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY34" t="n">
         <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7495,86 +7495,86 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>3.8</v>
+        <v>6.75</v>
       </c>
       <c r="Q36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S36" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD36" t="n">
         <v>2.7</v>
       </c>
-      <c r="R36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S36" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>2.18</v>
-      </c>
       <c r="AE36" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AG36" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="AI36" t="n">
-        <v>11</v>
+        <v>7.9</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK36" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP36" t="n">
         <v>1.45</v>
@@ -7583,13 +7583,13 @@
         <v>1.75</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AT36" t="n">
-        <v>4.28</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
         <v>2.5</v>
@@ -7598,40 +7598,40 @@
         <v>1.93</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AX36" t="n">
         <v>1.35</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.28</v>
+        <v>3.55</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.96</v>
+        <v>2.41</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.56</v>
+        <v>3.08</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7692,86 +7692,86 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>6.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="R37" t="n">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="S37" t="n">
-        <v>7.71</v>
+        <v>4.6</v>
       </c>
       <c r="T37" t="n">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="U37" t="n">
-        <v>2.07</v>
+        <v>2.9</v>
       </c>
       <c r="V37" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="W37" t="n">
-        <v>2.59</v>
+        <v>2.15</v>
       </c>
       <c r="X37" t="n">
-        <v>3.15</v>
+        <v>3.98</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="Z37" t="n">
-        <v>7.9</v>
+        <v>9.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.25</v>
+        <v>2.88</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AG37" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AI37" t="n">
-        <v>7.9</v>
+        <v>11</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK37" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AO37" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
         <v>1.45</v>
@@ -7780,13 +7780,13 @@
         <v>1.75</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AU37" t="n">
         <v>2.5</v>
@@ -7795,40 +7795,40 @@
         <v>1.93</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AX37" t="n">
         <v>1.35</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ37" t="n">
-        <v>3.55</v>
+        <v>2.28</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.41</v>
+        <v>2.96</v>
       </c>
       <c r="BD37" t="n">
-        <v>3.08</v>
+        <v>2.56</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46141.60416666666</v>
@@ -7899,7 +7899,7 @@
         <v>3.89</v>
       </c>
       <c r="R38" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="S38" t="n">
         <v>2.4</v>
@@ -7908,22 +7908,22 @@
         <v>2.38</v>
       </c>
       <c r="U38" t="n">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="V38" t="n">
         <v>1.22</v>
       </c>
       <c r="W38" t="n">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="X38" t="n">
         <v>2.18</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA38" t="n">
         <v>1.13</v>
@@ -7935,13 +7935,13 @@
         <v>1.15</v>
       </c>
       <c r="AD38" t="n">
-        <v>4.84</v>
+        <v>5.8</v>
       </c>
       <c r="AE38" t="n">
         <v>1.48</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG38" t="n">
         <v>2.16</v>
@@ -7962,7 +7962,7 @@
         <v>2.3</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AN38" t="n">
         <v>1.83</v>
@@ -7971,13 +7971,13 @@
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AS38" t="n">
         <v>2.42</v>
@@ -7992,13 +7992,13 @@
         <v>2.28</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AZ38" t="n">
         <v>1.61</v>
@@ -8016,7 +8016,7 @@
         <v>4.5</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="BF38" t="n">
         <v>1.25</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8887,13 +8887,13 @@
         <v>6</v>
       </c>
       <c r="S43" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="T43" t="n">
         <v>2.38</v>
       </c>
       <c r="U43" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="V43" t="n">
         <v>1.28</v>
@@ -8917,13 +8917,13 @@
         <v>1.03</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AD43" t="n">
         <v>3.98</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AF43" t="n">
         <v>2.07</v>
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R44" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9320,7 +9320,7 @@
         <v>1.85</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AG45" t="n">
         <v>3.14</v>
@@ -9335,10 +9335,10 @@
         <v>1.09</v>
       </c>
       <c r="AK45" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AM45" t="n">
         <v>1.15</v>
@@ -9398,7 +9398,7 @@
         <v>1.64</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9678,10 +9678,10 @@
         <v>3.1</v>
       </c>
       <c r="T47" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="U47" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="V47" t="n">
         <v>1.34</v>
@@ -9690,25 +9690,25 @@
         <v>2.75</v>
       </c>
       <c r="X47" t="n">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Z47" t="n">
         <v>5.6</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AB47" t="n">
         <v>1</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AD47" t="n">
-        <v>3.78</v>
+        <v>3.25</v>
       </c>
       <c r="AE47" t="n">
         <v>1.7</v>
@@ -9720,13 +9720,13 @@
         <v>3.1</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AI47" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK47" t="n">
         <v>1.68</v>
@@ -9735,10 +9735,10 @@
         <v>2.02</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9780,19 +9780,19 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BC47" t="n">
         <v>1.93</v>
       </c>
       <c r="BD47" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE47" t="n">
         <v>1.76</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>

--- a/jogos_2026-04-29.xlsx
+++ b/jogos_2026-04-29.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.17</v>
+        <v>2.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="S22" t="n">
-        <v>4.08</v>
+        <v>3.35</v>
       </c>
       <c r="T22" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="U22" t="n">
         <v>3.02</v>
       </c>
       <c r="V22" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="W22" t="n">
-        <v>2.44</v>
+        <v>2.85</v>
       </c>
       <c r="X22" t="n">
-        <v>2.99</v>
+        <v>2.68</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z22" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AI22" t="n">
-        <v>6.65</v>
+        <v>4.75</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.9</v>
+        <v>2.17</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.36</v>
+        <v>4.05</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,28 +5135,28 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.6</v>
+        <v>1.98</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="S24" t="n">
-        <v>3.35</v>
+        <v>2.55</v>
       </c>
       <c r="T24" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="U24" t="n">
-        <v>3.02</v>
+        <v>4.11</v>
       </c>
       <c r="V24" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="X24" t="n">
         <v>2.62</v>
@@ -5165,49 +5165,49 @@
         <v>1.42</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="AA24" t="n">
         <v>1.06</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.5</v>
+        <v>3.87</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AF24" t="n">
         <v>1.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="AH24" t="n">
         <v>1.33</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.37</v>
+        <v>5.25</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.41</v>
+        <v>1.74</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,16 +5249,16 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.05</v>
+        <v>3.92</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="BF24" t="n">
         <v>1.18</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.95</v>
+        <v>6</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="R25" t="n">
-        <v>3.43</v>
+        <v>1.48</v>
       </c>
       <c r="S25" t="n">
-        <v>2.55</v>
+        <v>5.35</v>
       </c>
       <c r="T25" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="U25" t="n">
-        <v>4.11</v>
+        <v>1.81</v>
       </c>
       <c r="V25" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="W25" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="X25" t="n">
-        <v>2.62</v>
+        <v>2.08</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="Z25" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.95</v>
+        <v>2.7</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.02</v>
+        <v>2.1</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="AI25" t="n">
-        <v>5.25</v>
+        <v>3.7</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.09</v>
+        <v>2.32</v>
       </c>
       <c r="AM25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN25" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.19</v>
+        <v>1.08</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.01</v>
+        <v>1.65</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.92</v>
+        <v>5.65</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.74</v>
+        <v>2.13</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6120,19 +6120,19 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
         <v>2.37</v>
       </c>
       <c r="S29" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="T29" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="U29" t="n">
         <v>3.1</v>
@@ -6159,25 +6159,25 @@
         <v>1.04</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AD29" t="n">
         <v>3.9</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.49</v>
+        <v>1.71</v>
       </c>
       <c r="AF29" t="n">
         <v>2.08</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AH29" t="n">
         <v>1.36</v>
       </c>
       <c r="AI29" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AJ29" t="n">
         <v>1.11</v>
@@ -6186,13 +6186,13 @@
         <v>1.57</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AM29" t="n">
         <v>1.46</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.91</v>
+        <v>2.27</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>2.69</v>
       </c>
       <c r="R31" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="S31" t="n">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="U31" t="n">
-        <v>4.33</v>
+        <v>4.77</v>
       </c>
       <c r="V31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AF31" t="n">
         <v>1.36</v>
       </c>
-      <c r="W31" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AG31" t="n">
-        <v>2.89</v>
+        <v>5.75</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="AI31" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.62</v>
+        <v>2.23</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.04</v>
+        <v>1.57</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="AS31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV31" t="n">
         <v>2.1</v>
       </c>
-      <c r="AT31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AW31" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.02</v>
+        <v>2.78</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.92</v>
+        <v>2.66</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.74</v>
+        <v>1.36</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.27</v>
+        <v>1.91</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.69</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="T32" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="U32" t="n">
-        <v>4.77</v>
+        <v>4.33</v>
       </c>
       <c r="V32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W32" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK32" t="n">
         <v>1.62</v>
       </c>
-      <c r="W32" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>2.23</v>
-      </c>
       <c r="AL32" t="n">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="AM32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BB32" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN32" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AR32" t="n">
+      <c r="BC32" t="n">
         <v>2.02</v>
       </c>
-      <c r="AS32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.78</v>
-      </c>
       <c r="BD32" t="n">
-        <v>2.66</v>
+        <v>3.92</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.36</v>
+        <v>1.74</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.91</v>
+        <v>1.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.89</v>
+        <v>12</v>
       </c>
       <c r="R38" t="n">
-        <v>3.6</v>
+        <v>23.19</v>
       </c>
       <c r="S38" t="n">
-        <v>2.4</v>
+        <v>1.34</v>
       </c>
       <c r="T38" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="U38" t="n">
-        <v>3.84</v>
+        <v>12.2</v>
       </c>
       <c r="V38" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="W38" t="n">
-        <v>3.48</v>
+        <v>5.3</v>
       </c>
       <c r="X38" t="n">
-        <v>2.18</v>
+        <v>1.77</v>
       </c>
       <c r="Y38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AL38" t="n">
         <